--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="簡體合集包" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$I$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'簡體合集包'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>系統介面、模組、合集包（繁體）三個倉庫一起比，共 124 條。玩家最常看到的排在最上面。</t>
+          <t>系統介面、模組、合集包（繁體）三個倉庫一起比，共 139 條。玩家最常看到的排在最上面。</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>有建議譯名（50 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
+          <t>有建議譯名（54 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>待裁定（74 條）。拿不準，需要人來決定。</t>
+          <t>待裁定（85 條）。拿不準，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>泥怪</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>合集包的規則內文寫「泥怪」62 次，「泥形生物」只有 2 次，玩家讀規則時看到的是前者。</t>
+          <t>2 個倉庫都用「泥怪」，只有 compendium 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>類人怪物</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1615,14 +1615,14 @@
           <t>人形怪物</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>類人怪物</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>兩種說法各有人用；合集包內文「人形怪物」27 次、「類人怪物」24 次，差距不夠大，需要人來決定。</t>
+          <t>2 個倉庫都用「類人怪物」，只有 compendium 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Wayang</t>
+          <t>Kami</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>皮影人</t>
+          <t>神靈</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>神</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>剪影人</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>剪影人</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>合集包的規則內文寫「剪影人」30 次，「皮影人」只有 0 次，玩家讀規則時看到的是前者。</t>
+          <t>「神」是「神靈」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Ratfolk</t>
+          <t>Extraplanar</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -1692,27 +1692,27 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>鼠族</t>
+          <t>跨位面</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>異界</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>鼠人</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>鼠族</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>合集包的規則內文寫「鼠族」17 次，「鼠人」只有 3 次，玩家讀規則時看到的是前者。</t>
+          <t>「異界」也出現在「異界生物」（Outsider）這類詞裡，內文次數會灌水，不能當證據，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1722,22 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Bonus Feats</t>
+          <t>Wayang</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>皮影人</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -1747,18 +1747,17 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>獎勵專長×5
-額外專長</t>
+          <t>剪影人</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>獎勵專長</t>
+          <t>剪影人</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>「獎勵專長」用了 5 次，另一種只有 1 次，照多數。</t>
+          <t>合集包的規則內文寫「剪影人」30 次，「皮影人」只有 0 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -1768,43 +1767,42 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Ki Pool</t>
+          <t>Troop</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>部隊</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>軍隊</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>氣池×3
-氣運丹田</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>氣池</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>「氣池」用了 3 次，另一種只有 1 次，照多數。</t>
+          <t>「軍隊」是一般用字，內文次數不能當證據，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -1814,43 +1812,42 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>機體</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>機器人</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>專長×2
-忍法·心技體</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>專長</t>
+          <t>機體</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>「忍法·心技體」是忍者版刻意取的風格名，但通用的 Feat 就叫「專長」，三個倉庫都這樣用。</t>
+          <t>合集包的規則內文寫「機體」20 次，「機器人」只有 3 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -1860,642 +1857,632 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
+          <t>Leshy</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>萊西</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>勒席</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>萊西</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>合集包的規則內文寫「萊西」20 次，「勒席」只有 0 次，玩家讀規則時看到的是前者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Ratfolk</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>鼠族</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>鼠人</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>鼠族</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>合集包的規則內文寫「鼠族」17 次，「鼠人」只有 3 次，玩家讀規則時看到的是前者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Azata</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>靈使</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>愛塔天族</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>靈使</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>合集包的規則內文寫「靈使」10 次，「愛塔天族」只有 0 次，玩家讀規則時看到的是前者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Archon</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>聖使</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>亞空天族</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Agathion</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>衛使</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>蓋丁天族</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Div</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>妖靈</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>迪瓦</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Derro</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>迪洛人</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>迪洛矮人</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Dark Folk</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>幽暗之民</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>暗黑民</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Demodand</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>神孽</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>泰坦神孽</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>「神孽」是「泰坦神孽」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Spawn of Rovagug</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>種族／生物類型</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>拉瓦古格之嗣</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>拉瓦古格之子</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Bonus Feats</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>獎勵專長×5
+額外專長</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>獎勵專長</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>「獎勵專長」用了 5 次，另一種只有 1 次，照多數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Ki Pool</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>氣池×3
+氣運丹田</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>氣池</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>「氣池」用了 3 次，另一種只有 1 次，照多數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>專長×2
+忍法·心技體</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>專長</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>「忍法·心技體」是忍者版刻意取的風格名，但通用的 Feat 就叫「專長」，三個倉庫都這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
           <t>Rogue Talent</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>倉內不一致</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>忍法·身合
 遊蕩者天賦
 盜賊天賦</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>職業名 Rogue 譯作「遊蕩者」，但合集包內文寫「盜賊天賦」57 次、「遊蕩者天賦」只有 5 次，兩邊打架；另外沒標職業的通用條目被譯成忍者風格的「忍法·身合」，看起來是誤植。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Spontaneous Casting</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>自發施法×2
-法術轉換</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>自發施法</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「自發施法」29 次，「法術轉換」只有 6 次，玩家讀規則時看到的是前者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Amazing Inspiration</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>驚人靈感
-奇妙靈感</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>奇妙靈感</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>奇妙靈感</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「奇妙靈感」，只有 mods 另有寫法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>True Inspiration</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>真實靈感
-靈感滿溢</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>靈感滿溢</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>靈感滿溢</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「靈感滿溢」，只有 mods 另有寫法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Tenacious Inspiration</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>頑強靈感
-執著靈感</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>執著靈感</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>執著靈感</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「執著靈感」，只有 mods 另有寫法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Maneuver Mastery</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>戰技熟稔×2
-戰技精通</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Unarmed Strike</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>徒手擊打
-徒手打擊</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法各有人用；合集包內文「徒手打擊」276 次、「徒手擊打」140 次，差距不夠大，需要人來決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Increased Damage Reduction</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>傷害減免
-增強傷害減免</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>「傷害減免」是「增強傷害減免」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>引導能量
-能量引導</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>引導能量</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「引導能量」179 次，「能量引導」只有 3 次，玩家讀規則時看到的是前者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>Low-Light Vision</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>低光視力
-昏暗視覺</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>昏暗視覺</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「昏暗視覺」158 次，「低光視力」只有 1 次，玩家讀規則時看到的是前者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Breath Weapon</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>噴吐武器
-噴吐龍息</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>噴吐武器</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「噴吐武器」102 次，「噴吐龍息」只有 0 次，玩家讀規則時看到的是前者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Wings</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>翅膀
-龍翼</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>「翅膀」是一般用字，內文次數不能當證據；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Evasion</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>忍法·無常步
-反射閃避</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Knockback</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>一擊即飛
-擊飛</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>擊飛</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「擊飛」27 次，「一擊即飛」只有 0 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2492,7 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Elemental Body</t>
+          <t>Spontaneous Casting</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -2530,18 +2517,18 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>元素之軀
-元素身軀</t>
+          <t>自發施法×2
+法術轉換</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>元素身軀</t>
+          <t>自發施法</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>合集包的規則內文寫「元素身軀」12 次，「元素之軀」只有 0 次，玩家讀規則時看到的是前者。</t>
+          <t>合集包的規則內文寫「自發施法」29 次，「法術轉換」只有 6 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2538,7 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Superstition</t>
+          <t>Amazing Inspiration</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -2561,7 +2548,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -2571,23 +2558,23 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>驚人靈感
+奇妙靈感</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>神秘迷信
-迷信</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>奇妙靈感</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>奇妙靈感</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>「迷信」是「神秘迷信」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>2 個倉庫都用「奇妙靈感」，只有 mods 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2584,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Abundant Step</t>
+          <t>True Inspiration</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -2607,7 +2594,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -2617,23 +2604,23 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>真實靈感
+靈感滿溢</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>天遁術
-遁術</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>靈感滿溢</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>靈感滿溢</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>「遁術」是「天遁術」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>2 個倉庫都用「靈感滿溢」，只有 mods 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2630,7 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Major Magic</t>
+          <t>Tenacious Inspiration</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -2653,7 +2640,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -2663,23 +2650,23 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>頑強靈感
+執著靈感</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>高等魔法
-高級魔法</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>執著靈感</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>執著靈感</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>2 個倉庫都用「執著靈感」，只有 mods 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2676,7 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Minor Magic</t>
+          <t>Maneuver Mastery</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -2714,8 +2701,8 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>次等魔法
-次級魔法</t>
+          <t>戰技熟稔×2
+戰技精通</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -2735,7 +2722,7 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Order of the Beast</t>
+          <t>Unarmed Strike</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -2760,8 +2747,8 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>獸之騎士團
-狂獸騎士團</t>
+          <t>徒手擊打
+徒手打擊</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -2771,7 +2758,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>兩種說法各有人用；合集包內文「徒手打擊」276 次、「徒手擊打」140 次，差距不夠大，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2768,7 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Resiliency</t>
+          <t>Increased Damage Reduction</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -2806,8 +2793,8 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>堅韌身軀
-韌性</t>
+          <t>傷害減免
+增強傷害減免</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -2817,7 +2804,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「傷害減免」是「增強傷害減免」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2814,7 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Acid Dart</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -2852,18 +2839,18 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>強酸鏢
-酸鏢</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>引導能量
+能量引導</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>引導能量</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>合集包的規則內文寫「引導能量」179 次，「能量引導」只有 3 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2860,7 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Intimidating Glare</t>
+          <t>Spirit</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -2883,7 +2870,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -2893,13 +2880,12 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>精魂</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>威嚇凝視
-威嚇怒視</t>
+          <t>魂域</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -2909,7 +2895,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>兩種說法各有人用；合集包內文「精魂」98 次、「魂域」69 次，差距不夠大，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2905,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Smoke Bomb</t>
+          <t>Low-Light Vision</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -2944,18 +2930,18 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>忍法·迷蹤
-煙霧炸彈</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>低光視力
+昏暗視覺</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>昏暗視覺</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
+          <t>合集包的規則內文寫「昏暗視覺」158 次，「低光視力」只有 1 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2951,7 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Guarded Stance</t>
+          <t>Breath Weapon</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -2990,18 +2976,18 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>守衛姿態
-防衛戰姿</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>噴吐武器
+噴吐龍息</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>噴吐武器</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>合集包的規則內文寫「噴吐武器」102 次，「噴吐龍息」只有 0 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -3011,7 +2997,7 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Terrifying Howl</t>
+          <t>Wings</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -3036,8 +3022,8 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>可怖狂嚎
-怖懼狂嚎</t>
+          <t>翅膀
+龍翼</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -3047,7 +3033,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「翅膀」是一般用字，內文次數不能當證據；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3043,7 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Animal Fury</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -3082,8 +3068,8 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>獸性之怒
-野性之怒</t>
+          <t>忍法·無常步
+反射閃避</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -3093,7 +3079,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3089,7 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Aura of Despair</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -3113,7 +3099,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -3123,13 +3109,12 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>秘示</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>絕望光環
-絕望靈光</t>
+          <t>秘示域</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -3139,7 +3124,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「秘示」是「秘示域」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3134,7 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Auspicious Mark</t>
+          <t>Knockback</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -3174,18 +3159,18 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>吉祥印記
-吉祥烙記</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>一擊即飛
+擊飛</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>擊飛</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>合集包的規則內文寫「擊飛」27 次，「一擊即飛」只有 0 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3180,7 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Deadly Accuracy</t>
+          <t>Elemental Body</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -3220,18 +3205,18 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>死亡精準
-致命精確</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>元素之軀
+元素身軀</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>元素身軀</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>合集包的規則內文寫「元素身軀」12 次，「元素之軀」只有 0 次，玩家讀規則時看到的是前者。</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3226,7 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>High Jump</t>
+          <t>Superstition</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -3266,8 +3251,8 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>輕功
-輕身縱</t>
+          <t>神秘迷信
+迷信</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -3277,7 +3262,7 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「迷信」是「神秘迷信」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3272,7 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Poison Resistance</t>
+          <t>Abundant Step</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -3312,8 +3297,8 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>毒素抗力
-毒性抗力</t>
+          <t>天遁術
+遁術</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -3323,7 +3308,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「遁術」是「天遁術」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3318,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Dazing Touch</t>
+          <t>Major Magic</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -3358,8 +3343,8 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>恍惚接觸
-眩目之觸</t>
+          <t>高等魔法
+高級魔法</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -3379,7 +3364,7 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Ground Breaker</t>
+          <t>Minor Magic</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -3404,8 +3389,8 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>大地之擊
-撼地一擊</t>
+          <t>次等魔法
+次級魔法</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3425,7 +3410,7 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Skill Mastery</t>
+          <t>Order of the Beast</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -3450,8 +3435,8 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>技能專精
-技藝精湛</t>
+          <t>獸之騎士團
+狂獸騎士團</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3471,7 +3456,7 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Swift Foot</t>
+          <t>Resiliency</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -3496,8 +3481,8 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>迅捷腳步
-迅足</t>
+          <t>堅韌身軀
+韌性</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -3517,7 +3502,7 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Bardic Knowledge</t>
+          <t>Acid Dart</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -3542,8 +3527,8 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>軼聞知識
-逸聞知識</t>
+          <t>強酸鏢
+酸鏢</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3553,7 +3538,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3548,7 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Bleeding Blow</t>
+          <t>Intimidating Glare</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -3588,8 +3573,8 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>出血打擊
-流血猛擊</t>
+          <t>威嚇凝視
+威嚇怒視</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -3609,7 +3594,7 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Crippling Blow</t>
+          <t>Smoke Bomb</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -3634,8 +3619,8 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>致殘打擊
-致殘猛擊</t>
+          <t>忍法·迷蹤
+煙霧炸彈</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -3645,7 +3630,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3640,7 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Eater of Magic</t>
+          <t>Guarded Stance</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -3680,8 +3665,8 @@
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>享用魔力
-吞噬魔法</t>
+          <t>守衛姿態
+防衛戰姿</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3701,7 +3686,7 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Lasting Poison</t>
+          <t>Terrifying Howl</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -3726,8 +3711,8 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>持久毒藥
-毒性持續</t>
+          <t>可怖狂嚎
+怖懼狂嚎</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3747,7 +3732,7 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Nimble Climber</t>
+          <t>Animal Fury</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -3772,8 +3757,8 @@
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>機敏攀巖者
-飛簷走壁</t>
+          <t>獸性之怒
+野性之怒</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3793,7 +3778,7 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Raging Leaper</t>
+          <t>Aura of Despair</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -3818,8 +3803,8 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>狂暴躍者
-狂暴跳躍</t>
+          <t>絕望光環
+絕望靈光</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3839,7 +3824,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Raging Swimmer</t>
+          <t>Auspicious Mark</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -3864,8 +3849,8 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>狂暴泳者
-狂暴遊者</t>
+          <t>吉祥印記
+吉祥烙記</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3885,7 +3870,7 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Sharpened Accuracy</t>
+          <t>Deadly Accuracy</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -3910,8 +3895,8 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>敏銳精準
-敏銳精確</t>
+          <t>死亡精準
+致命精確</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3931,7 +3916,7 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Sprint</t>
+          <t>High Jump</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -3956,8 +3941,8 @@
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>奮力衝刺
-奮勇衝刺</t>
+          <t>輕功
+輕身縱</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3977,7 +3962,7 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Sudden Speed</t>
+          <t>Poison Resistance</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -4002,8 +3987,8 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>瞬時加速
-電瞬步</t>
+          <t>毒素抗力
+毒性抗力</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -4023,7 +4008,7 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Unexpected Strike</t>
+          <t>Dazing Touch</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -4048,8 +4033,8 @@
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>意外之擊
-詭擊</t>
+          <t>恍惚接觸
+眩目之觸</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -4069,7 +4054,7 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Witch Hunter</t>
+          <t>Ground Breaker</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -4094,8 +4079,8 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>女巫獵人
-獵巫人</t>
+          <t>大地之擊
+撼地一擊</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -4115,7 +4100,7 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Aberrant Form</t>
+          <t>Skill Mastery</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -4140,8 +4125,8 @@
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>化身異怪
-異怪形態</t>
+          <t>技能專精
+技藝精湛</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -4161,7 +4146,7 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Brain Drain</t>
+          <t>Swift Foot</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -4186,8 +4171,8 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>意識鑽刺
-意識鑽探</t>
+          <t>迅捷腳步
+迅足</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4207,7 +4192,7 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Clear Mind</t>
+          <t>Bardic Knowledge</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -4232,8 +4217,8 @@
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>心如堅鋼
-心若明鏡</t>
+          <t>軼聞知識
+逸聞知識</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4253,7 +4238,7 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Fearless Rage</t>
+          <t>Bleeding Blow</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -4278,8 +4263,8 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>無懼狂暴
-無畏狂暴</t>
+          <t>出血打擊
+流血猛擊</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -4299,7 +4284,7 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Flesh Wound</t>
+          <t>Crippling Blow</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
@@ -4324,8 +4309,8 @@
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>不屈武勇
-皮外小傷</t>
+          <t>致殘打擊
+致殘猛擊</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -4345,7 +4330,7 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Improved Quarry</t>
+          <t>Eater of Magic</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -4370,8 +4355,8 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>精通狩獵目標
-高等狩獵目標</t>
+          <t>享用魔力
+吞噬魔法</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -4391,7 +4376,7 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Inspire Ferocity</t>
+          <t>Lasting Poison</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -4416,8 +4401,8 @@
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>狂怒之示
-狂怒激發</t>
+          <t>持久毒藥
+毒性持續</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -4437,7 +4422,7 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Lethal Accuracy</t>
+          <t>Nimble Climber</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -4462,8 +4447,8 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>致命精準
-致死精確</t>
+          <t>機敏攀巖者
+飛簷走壁</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -4483,7 +4468,7 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Life Sight</t>
+          <t>Raging Leaper</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
@@ -4508,8 +4493,8 @@
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>感知生命
-生命視野</t>
+          <t>狂暴躍者
+狂暴跳躍</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4529,7 +4514,7 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Light Steps</t>
+          <t>Raging Swimmer</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -4554,8 +4539,8 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>凌波步
-輕身步</t>
+          <t>狂暴泳者
+狂暴遊者</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4575,7 +4560,7 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Quick Reflexes</t>
+          <t>Sharpened Accuracy</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
@@ -4600,8 +4585,8 @@
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>快速反射
-超速反射</t>
+          <t>敏銳精準
+敏銳精確</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -4621,7 +4606,7 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Roused Anger</t>
+          <t>Sprint</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -4646,8 +4631,8 @@
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>無邊怒火
-激發怒意</t>
+          <t>奮力衝刺
+奮勇衝刺</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4667,7 +4652,7 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Slowing Strike</t>
+          <t>Sudden Speed</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
@@ -4692,8 +4677,8 @@
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>延緩打擊
-遲緩一擊</t>
+          <t>瞬時加速
+電瞬步</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -4713,7 +4698,7 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Smasher</t>
+          <t>Unexpected Strike</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -4738,8 +4723,8 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>破壞者
-野蠻破壞</t>
+          <t>意外之擊
+詭擊</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4759,32 +4744,33 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>（文本）</t>
+          <t>Witch Hunter</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>文本×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>文本×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>文本×384</t>
+          <t>女巫獵人
+獵巫人</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4794,7 +4780,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>合集包多是法術欄位的「見文本」（see text），系統介面是「文本頁」；台灣一般說「內文」，但倉庫裡還沒有現成寫法。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4804,17 +4790,17 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>（信息）</t>
+          <t>Aberrant Form</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
@@ -4829,17 +4815,18 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>信息×211</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="inlineStr">
-        <is>
-          <t>訊息</t>
+          <t>化身異怪
+異怪形態</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「訊息」，mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4849,17 +4836,17 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>（激活）</t>
+          <t>Brain Drain</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
@@ -4874,17 +4861,18 @@
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>激活×59</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="inlineStr">
-        <is>
-          <t>啟動</t>
+          <t>意識鑽刺
+意識鑽探</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>全是合集包內文的「激活某能力」；合集包已有 197 處寫「啟動」。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4894,42 +4882,43 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>（圖標）</t>
+          <t>Clear Mind</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>圖標×12</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>圖標×25</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>圖標×3</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="inlineStr">
-        <is>
-          <t>圖示</t>
+          <t>心如堅鋼
+心若明鏡</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「圖示」，mods 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4939,22 +4928,22 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>（設置）</t>
+          <t>Fearless Rage</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>設置×33</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -4964,17 +4953,18 @@
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="inlineStr">
-        <is>
-          <t>設定</t>
+          <t>無懼狂暴
+無畏狂暴</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「設定」，mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4984,17 +4974,17 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>（添加）</t>
+          <t>Flesh Wound</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -5009,7 +4999,8 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>添加×29</t>
+          <t>不屈武勇
+皮外小傷</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -5019,7 +5010,7 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>這些是規則內文的「添加到加值上」，改不改看語氣；介面上的「添加」早就統一成「新增」了。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5020,17 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>（复）</t>
+          <t>Improved Quarry</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
@@ -5054,17 +5045,18 @@
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>复×27</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="inlineStr">
-        <is>
-          <t>復</t>
+          <t>精通狩獵目標
+高等狩獵目標</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>「复」是簡體字，同一個詞在倉庫其他地方已經寫成「復」。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5066,17 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>（數據）</t>
+          <t>Inspire Ferocity</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
@@ -5094,22 +5086,23 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>數據×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>數據×23</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>資料</t>
+          <t>狂怒之示
+狂怒激發</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「資料」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5119,17 +5112,17 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>（鏈接）</t>
+          <t>Lethal Accuracy</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
@@ -5144,17 +5137,18 @@
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>鏈接×25</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="inlineStr">
-        <is>
-          <t>連結</t>
+          <t>致命精準
+致死精確</t>
+        </is>
+      </c>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「連結」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5164,17 +5158,17 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>（質量）</t>
+          <t>Life Sight</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
@@ -5189,17 +5183,18 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>質量×24</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
-        <is>
-          <t>品質</t>
+          <t>感知生命
+生命視野</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「品質」，compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5209,17 +5204,17 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>（界面）</t>
+          <t>Light Steps</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
@@ -5229,12 +5224,13 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>界面×21</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>界面×2</t>
+          <t>凌波步
+輕身步</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -5244,7 +5240,7 @@
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「介面」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5254,17 +5250,17 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>（拖拽）</t>
+          <t>Quick Reflexes</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
@@ -5274,22 +5270,23 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>拖拽×22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="12" t="inlineStr">
-        <is>
-          <t>拖曳</t>
+          <t>快速反射
+超速反射</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「拖曳」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5299,42 +5296,43 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>（變量）</t>
+          <t>Roused Anger</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>變量×10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>變量×4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>變量×7</t>
-        </is>
-      </c>
-      <c r="H102" s="12" t="inlineStr">
-        <is>
-          <t>變數</t>
+          <t>無邊怒火
+激發怒意</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「變數」，compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5344,17 +5342,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>（窗口）</t>
+          <t>Slowing Strike</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
@@ -5364,12 +5362,13 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>窗口×10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>窗口×8</t>
+          <t>延緩打擊
+遲緩一擊</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -5379,7 +5378,7 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「視窗」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5389,22 +5388,22 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>（自定義）</t>
+          <t>Smasher</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>自定義×16</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -5414,17 +5413,18 @@
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>自定義×1</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="inlineStr">
-        <is>
-          <t>自訂</t>
+          <t>破壞者
+野蠻破壞</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「自訂」，mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>（全局）</t>
+          <t>（文本）</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -5449,27 +5449,27 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>全局×1</t>
+          <t>文本×8</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>全局×14</t>
+          <t>文本×8</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="inlineStr">
-        <is>
-          <t>全域</t>
+          <t>文本×384</t>
+        </is>
+      </c>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「全域」，mods、compendium 已經這樣用。</t>
+          <t>合集包多是法術欄位的「見文本」（see text），系統介面是「文本頁」；台灣一般說「內文」，但倉庫裡還沒有現成寫法。</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>（創建）</t>
+          <t>（信息）</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>創建×14</t>
+          <t>信息×211</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>建立</t>
+          <t>訊息</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「建立」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「訊息」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>（用戶）</t>
+          <t>（激活）</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -5539,27 +5539,27 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>用戶×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>用戶×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>激活×59</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>使用者</t>
+          <t>啟動</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「使用者」，mods、compendium 已經這樣用。</t>
+          <t>全是合集包內文的「激活某能力」；合集包已有 197 處寫「啟動」。</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>（調試）</t>
+          <t>（圖標）</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
@@ -5584,27 +5584,27 @@
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>圖標×12</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>調試×8</t>
+          <t>圖標×25</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H108" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>圖標×3</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>圖示</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「偵錯」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣寫「圖示」，mods 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>（控件）</t>
+          <t>（設置）</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>設置×33</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>控件×6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
@@ -5642,14 +5642,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H109" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>設定</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「控制項」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣寫「設定」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>（運行）</t>
+          <t>（添加）</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
@@ -5674,27 +5674,27 @@
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>運行×3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>運行×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="inlineStr">
-        <is>
-          <t>執行</t>
+          <t>添加×29</t>
+        </is>
+      </c>
+      <c r="H110" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「執行」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>這些是規則內文的「添加到加值上」，改不改看語氣；介面上的「添加」早就統一成「新增」了。</t>
         </is>
       </c>
     </row>
@@ -5704,17 +5704,17 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>（令牌）</t>
+          <t>（复）</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -5724,22 +5724,22 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>令牌×4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>复×27</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>指示物</t>
+          <t>復</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「指示物」，pf1-zhtw、mods 已經這樣用。</t>
+          <t>「复」是簡體字，同一個詞在倉庫其他地方已經寫成「復」。</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>（字段）</t>
+          <t>（數據）</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
@@ -5769,22 +5769,22 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>字段×4</t>
+          <t>數據×2</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>數據×23</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>欄位</t>
+          <t>資料</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「欄位」，pf1-zhtw、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「資料」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>（默認）</t>
+          <t>（鏈接）</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -5819,17 +5819,17 @@
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>默認×4</t>
+          <t>鏈接×25</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>預設</t>
+          <t>連結</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「預設」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「連結」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>（搜索）</t>
+          <t>（質量）</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>搜索×3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -5864,17 +5864,17 @@
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>質量×24</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>搜尋</t>
+          <t>品質</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「搜尋」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「品質」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>（兼容）</t>
+          <t>（界面）</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -5899,27 +5899,27 @@
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>兼容×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>界面×21</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>兼容×1</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="inlineStr">
-        <is>
-          <t>相容</t>
+          <t>界面×2</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「相容」，mods 已經這樣用。</t>
+          <t>對岸用語；台灣一般寫「介面」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>（代碼）</t>
+          <t>（拖拽）</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
@@ -5944,27 +5944,27 @@
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>代碼×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>拖拽×22</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>代碼×1</t>
-        </is>
-      </c>
-      <c r="H116" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>拖曳</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「程式碼」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣寫「拖曳」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>（批量）</t>
+          <t>（變量）</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -5989,27 +5989,27 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>變量×10</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>批量×2</t>
+          <t>變量×4</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H117" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>變量×7</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>變數</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「批次」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣寫「變數」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>（攝像機）</t>
+          <t>（窗口）</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>攝像機×2</t>
+          <t>窗口×10</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>窗口×8</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「攝影機」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣一般寫「視窗」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>（粘貼）</t>
+          <t>（自定義）</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>自定義×16</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>粘貼×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>自定義×1</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>貼上</t>
+          <t>自訂</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「貼上」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「自訂」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>（刷新）</t>
+          <t>（全局）</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
@@ -6124,27 +6124,27 @@
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>全局×1</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>全局×14</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>刷新×2</t>
-        </is>
-      </c>
-      <c r="H120" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>全域</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>這裡是「刷新持續時間」（重新計時），介面用的「重新整理」不適用，需要人看語境。</t>
+          <t>對岸用語；台灣寫「全域」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6154,17 +6154,17 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>（钟）</t>
+          <t>（創建）</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>钟×2</t>
+          <t>創建×14</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>鐘</t>
+          <t>建立</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>「钟」是簡體字，同一個詞在倉庫其他地方已經寫成「鐘」。</t>
+          <t>對岸用語；台灣寫「建立」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>（導入）</t>
+          <t>（用戶）</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>導入×1</t>
+          <t>用戶×1</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>用戶×8</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>匯入</t>
+          <t>使用者</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「匯入」，mods 已經這樣用。</t>
+          <t>對岸用語；台灣寫「使用者」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>（服務器）</t>
+          <t>（調試）</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>服務器×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>調試×8</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「伺服器」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣一般寫「偵錯」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>（光標）</t>
+          <t>（控件）</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>光標×1</t>
+          <t>控件×6</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>對岸用語；台灣一般寫「游標」，但三個倉庫都還沒有這個寫法可對照。</t>
+          <t>對岸用語；台灣一般寫「控制項」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
       </c>
     </row>
@@ -6334,47 +6334,722 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
+          <t>（運行）</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>運行×3</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>運行×1</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>執行</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「執行」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>（令牌）</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>令牌×4</t>
+        </is>
+      </c>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>指示物</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「指示物」，pf1-zhtw、mods 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>（字段）</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>字段×4</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>欄位</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「欄位」，pf1-zhtw、compendium 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>（默認）</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>默認×4</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>預設</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「預設」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>（搜索）</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>搜索×3</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>搜尋</t>
+        </is>
+      </c>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「搜尋」，mods、compendium 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>（兼容）</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>兼容×2</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>兼容×1</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>相容</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「相容」，mods 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>（代碼）</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>代碼×1</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>代碼×1</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣一般寫「程式碼」，但三個倉庫都還沒有這個寫法可對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>（批量）</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>批量×2</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣一般寫「批次」，但三個倉庫都還沒有這個寫法可對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>（攝像機）</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>攝像機×2</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣一般寫「攝影機」，但三個倉庫都還沒有這個寫法可對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>（粘貼）</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>粘貼×2</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>貼上</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「貼上」，mods、compendium 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>（刷新）</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>刷新×2</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>這裡是「刷新持續時間」（重新計時），介面用的「重新整理」不適用，需要人看語境。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>（钟）</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>簡體字</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>簡體字</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>钟×2</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="inlineStr">
+        <is>
+          <t>鐘</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>「钟」是簡體字，同一個詞在倉庫其他地方已經寫成「鐘」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>（導入）</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>導入×1</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>匯入</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「匯入」，mods 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>（服務器）</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>服務器×1</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣一般寫「伺服器」，但三個倉庫都還沒有這個寫法可對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>（光標）</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>光標×1</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣一般寫「游標」，但三個倉庫都還沒有這個寫法可對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
           <t>（音頻）</t>
         </is>
       </c>
-      <c r="C125" s="11" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>對岸用語</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>對岸用語</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>音頻×1</t>
         </is>
       </c>
-      <c r="G125" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="inlineStr">
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
         <is>
           <t>音訊</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="I140" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「音訊」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I125"/>
+  <autoFilter ref="A1:I140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="簡體合集包" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$I$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$J$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'簡體合集包'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C15"/>
+  <dimension ref="B1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>有建議譯名（54 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
+          <t>有建議譯名（100 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>待裁定（85 條）。拿不準，需要人來決定。</t>
+          <t>待裁定（39 條）。拿不準，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -632,10 +632,22 @@
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>CHM 寫法</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CHM 線上版（chm.zhtrpg.com，v2.33.0）裡「中文（English）」的寫法與次數。標「（倉庫沒用）」的是 CHM 用了三個倉庫都沒有的寫法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>篩選</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>每一欄標題右邊有小箭頭，可以只看某個類別、只看「待裁定」等。</t>
         </is>
@@ -652,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -662,8 +674,9 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -707,10 +720,16 @@
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
+          <t>CHM v2.33.0
+寫法</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
           <t>建議採用</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
@@ -750,14 +769,19 @@
           <t>目盲</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>目盲×13</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>目盲</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「目盲」，只有 mods 另有寫法。</t>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「目盲（Blind）」13 次。</t>
         </is>
       </c>
     </row>
@@ -795,14 +819,19 @@
           <t>穩定</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>傷勢穩定</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「傷勢穩定」，只有 compendium 另有寫法。</t>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>穩定×2</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>穩定</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>CHM 的「狀態」頁寫「穩定（Stable）」。</t>
         </is>
       </c>
     </row>
@@ -840,14 +869,19 @@
           <t>能量汲取</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>能量流失</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「能量流失」，只有 compendium 另有寫法。</t>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>能量吸取×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>CHM 的「狀態」頁寫「能量吸取（Energy Drained）」，三個倉庫都沒用這個寫法；要不要改成 CHM 的說法，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -885,14 +919,20 @@
           <t>倒地</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法各有人用；合集包內文「俯臥」78 次、「倒地」77 次，差距不夠大，需要人來決定。</t>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>俯臥×10
+倒地×6</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>俯臥</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>CHM 的「狀態」頁寫「俯臥（Prone）」。</t>
         </is>
       </c>
     </row>
@@ -930,14 +970,20 @@
           <t>特技</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>「特技」是「特技動作」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>特技×20
+特技動作×6</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>特技</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「特技（Acrobatics）」20 次。</t>
         </is>
       </c>
     </row>
@@ -975,14 +1021,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>「臨時生命」是「臨時生命值」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>臨時生命值×2</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>臨時生命值</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「臨時生命值（Temporary Hit Points）」2 次。</t>
         </is>
       </c>
     </row>
@@ -1021,14 +1072,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>觸及×2</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>「觸及」是「長觸及」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>CHM 兩種都有（「觸及（Reach）」與「長觸及（Reach）」），系統介面裡兩個 Reach 是不同欄位，需要人看語境決定。</t>
         </is>
       </c>
     </row>
@@ -1067,14 +1123,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法各有人用；合集包內文「協助他人」41 次、「援助他人」17 次，差距不夠大，需要人來決定。</t>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>協助他人×4</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>協助他人</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「協助他人（Aid Another）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1175,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>「嫻熟」是「強制嫻熟」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>靈巧×8</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>靈巧</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「靈巧（Finesse）」8 次。</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1225,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>破武</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>「破損」已經是 Broken（破損狀態）的譯名，Sunder 再用「破損」會撞名。</t>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>擊破×10（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「擊破」，三個倉庫都沒用；另外系統介面的「破損」會跟 Broken（破損狀態）撞名，至少那個要改。</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1275,17 @@
           <t>盔甲專攻</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>護甲專攻</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>「護甲專攻」用了 3 次，另一種只有 1 次，照多數。</t>
         </is>
@@ -1250,14 +1326,19 @@
           <t>一擁而上</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>一擁而上×4</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>一擁而上</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「一擁而上」，只有 mods 另有寫法。</t>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「一擁而上（Gang Up）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1296,14 +1377,19 @@
           <t>沉著暴怒</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>沉著暴怒×4</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>沉著暴怒</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「沉著暴怒」，只有 mods 另有寫法。</t>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「沉著暴怒（Furious Focus）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1342,14 +1428,19 @@
           <t>包抄</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>包抄×8</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>包抄</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「包抄」，只有 mods 另有寫法。</t>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「包抄（Outflank）」8 次。</t>
         </is>
       </c>
     </row>
@@ -1388,14 +1479,19 @@
           <t>蛇行</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>蛇行×4</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>蛇行</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「蛇行」，只有 mods 另有寫法。</t>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「蛇行（Snake Sidewind）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1434,14 +1530,19 @@
           <t>武器專家</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>武器專家</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「武器專家」，只有 mods 另有寫法。</t>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>武術專精×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「武術專精」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1581,17 @@
           <t>靈感專注</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>靈感專注</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>2 個倉庫都用「靈感專注」，只有 mods 另有寫法。</t>
         </is>
@@ -1525,12 +1631,17 @@
           <t>進階盔甲專攻</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -1570,14 +1681,21 @@
           <t>泥形生物</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>泥怪×8
+泥形生物×2
+泥形怪物×4（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>泥怪</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「泥怪」，只有 compendium 另有寫法。</t>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「泥怪（Ooze）」8 次。</t>
         </is>
       </c>
     </row>
@@ -1615,14 +1733,20 @@
           <t>人形怪物</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>類人怪物</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「類人怪物」，只有 compendium 另有寫法。</t>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>人形怪物×7
+人型怪物×3（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>人形怪物</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「人形怪物（Monstrous Humanoid）」7 次。</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1784,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>「神」是「神靈」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>神靈×6</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>神靈</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「神靈（Kami）」6 次。</t>
         </is>
       </c>
     </row>
@@ -1705,14 +1834,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>「異界」也出現在「異界生物」（Outsider）這類詞裡，內文次數會灌水，不能當證據，需要人來決定。</t>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>CHM 沒有附英文的定名；「異界」也出現在「異界生物」（Outsider）裡，次數會灌水，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -1750,14 +1884,20 @@
           <t>剪影人</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>剪影人×6
+剪影語×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>剪影人</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「剪影人」30 次，「皮影人」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「剪影人（Wayang）」6 次。</t>
         </is>
       </c>
     </row>
@@ -1795,14 +1935,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>「軍隊」是一般用字，內文次數不能當證據，需要人來決定。</t>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>CHM 沒有附英文的定名；「軍隊」是一般用字，次數不能當證據，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -1840,14 +1985,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>機體</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「機體」20 次，「機器人」只有 3 次，玩家讀規則時看到的是前者。</t>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>機器人×2</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>機器人</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「機器人（Robot）」2 次。</t>
         </is>
       </c>
     </row>
@@ -1885,14 +2035,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>萊西×2</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>萊西</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「萊西」20 次，「勒席」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「萊西（Leshy）」2 次。</t>
         </is>
       </c>
     </row>
@@ -1930,14 +2085,20 @@
           <t>鼠人</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>鼠族×19
+鼠人×2</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>鼠族</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「鼠族」17 次，「鼠人」只有 3 次，玩家讀規則時看到的是前者。</t>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「鼠族（Ratfolk）」19 次。</t>
         </is>
       </c>
     </row>
@@ -1975,14 +2136,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>靈使×10</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>靈使</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「靈使」10 次，「愛塔天族」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「靈使（Azata）」10 次。</t>
         </is>
       </c>
     </row>
@@ -2020,14 +2186,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>聖使×2
+神使×9（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>CHM 多寫「神使」（9 次），三個倉庫都沒用這個寫法；現有寫法裡「聖使」在 CHM 出現 2 次。需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -2065,14 +2237,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>福使×26（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「福使」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -2110,14 +2287,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>妖靈×22</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>妖靈</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「妖靈（Div）」22 次。</t>
         </is>
       </c>
     </row>
@@ -2155,14 +2337,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>德洛人×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「德洛人」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2387,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -2245,14 +2437,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>魔孽×4（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>「神孽」是「泰坦神孽」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「魔孽」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2487,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -2336,14 +2538,19 @@
 額外專長</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>獎勵專長×89</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>獎勵專長</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>「獎勵專長」用了 5 次，另一種只有 1 次，照多數。</t>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「獎勵專長（Bonus Feats）」89 次。</t>
         </is>
       </c>
     </row>
@@ -2382,14 +2589,20 @@
 氣運丹田</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>氣池×8
+氣運丹田×2</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>氣池</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>「氣池」用了 3 次，另一種只有 1 次，照多數。</t>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「氣池（Ki Pool）」8 次。</t>
         </is>
       </c>
     </row>
@@ -2428,14 +2641,19 @@
 忍法·心技體</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>專長×172</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>專長</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>「忍法·心技體」是忍者版刻意取的風格名，但通用的 Feat 就叫「專長」，三個倉庫都這樣用。</t>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「專長（Feat）」172 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -2475,14 +2693,20 @@
 盜賊天賦</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>職業名 Rogue 譯作「遊蕩者」，但合集包內文寫「盜賊天賦」57 次、「遊蕩者天賦」只有 5 次，兩邊打架；另外沒標職業的通用條目被譯成忍者風格的「忍法·身合」，看起來是誤植。</t>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>盜賊天賦×29
+遊蕩者絕技×10（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>盜賊天賦</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「盜賊天賦（Rogue Talent）」29 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -2521,14 +2745,20 @@
 法術轉換</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>自發施法×16
+法術轉換×2</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>自發施法</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「自發施法」29 次，「法術轉換」只有 6 次，玩家讀規則時看到的是前者。</t>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「自發施法（Spontaneous Casting）」16 次。</t>
         </is>
       </c>
     </row>
@@ -2567,14 +2797,19 @@
           <t>奇妙靈感</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>奇妙靈感×2</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>奇妙靈感</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「奇妙靈感」，只有 mods 另有寫法。</t>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「奇妙靈感（Amazing Inspiration）」2 次。</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2848,17 @@
           <t>靈感滿溢</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>靈感滿溢</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>2 個倉庫都用「靈感滿溢」，只有 mods 另有寫法。</t>
         </is>
@@ -2659,14 +2899,19 @@
           <t>執著靈感</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>執著靈感×2</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>執著靈感</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「執著靈感」，只有 mods 另有寫法。</t>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「執著靈感（Tenacious Inspiration）」2 次。</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2950,17 @@
 戰技精通</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -2751,14 +3001,20 @@
 徒手打擊</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法各有人用；合集包內文「徒手打擊」276 次、「徒手擊打」140 次，差距不夠大，需要人來決定。</t>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>徒手打擊×22
+徒手擊打×2</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>徒手打擊</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
         </is>
       </c>
     </row>
@@ -2797,14 +3053,19 @@
 增強傷害減免</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>「傷害減免」是「增強傷害減免」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>增強傷害減免×20</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>增強傷害減免</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「增強傷害減免（Increased Damage Reduction）」20 次。</t>
         </is>
       </c>
     </row>
@@ -2843,14 +3104,19 @@
 能量引導</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>能量引導×2</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>引導能量</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「引導能量」179 次，「能量引導」只有 3 次，玩家讀規則時看到的是前者。</t>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>CHM 內文寫「引導能量」759 次、「能量引導」40 次。</t>
         </is>
       </c>
     </row>
@@ -2888,14 +3154,20 @@
           <t>魂域</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>魂域×4
+英靈×24（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法各有人用；合集包內文「精魂」98 次、「魂域」69 次，差距不夠大，需要人來決定。</t>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>CHM 多寫「英靈」（24 次），三個倉庫都沒用這個寫法；現有寫法裡「魂域」在 CHM 出現 4 次。需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -2934,14 +3206,19 @@
 昏暗視覺</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>昏暗視覺×102</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>昏暗視覺</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「昏暗視覺」158 次，「低光視力」只有 1 次，玩家讀規則時看到的是前者。</t>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「昏暗視覺（Low-Light Vision）」102 次。</t>
         </is>
       </c>
     </row>
@@ -2980,14 +3257,20 @@
 噴吐龍息</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>噴吐武器×6
+吐息武器×4（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>噴吐武器</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「噴吐武器」102 次，「噴吐龍息」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「噴吐武器（Breath Weapon）」6 次。</t>
         </is>
       </c>
     </row>
@@ -3026,14 +3309,19 @@
 龍翼</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>翅膀×2</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>「翅膀」是一般用字，內文次數不能當證據；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3072,14 +3360,19 @@
 反射閃避</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>反射閃避×20</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>反射閃避</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「反射閃避（Evasion）」20 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -3117,14 +3410,19 @@
           <t>秘示域</t>
         </is>
       </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>「秘示」是「秘示域」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>秘示域×12</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>秘示域</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「秘示域（Mystery）」12 次。</t>
         </is>
       </c>
     </row>
@@ -3163,14 +3461,19 @@
 擊飛</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>擊飛×8</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
         <is>
           <t>擊飛</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「擊飛」27 次，「一擊即飛」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「擊飛（Knockback）」8 次。</t>
         </is>
       </c>
     </row>
@@ -3209,14 +3512,19 @@
 元素身軀</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>元素身軀</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>合集包的規則內文寫「元素身軀」12 次，「元素之軀」只有 0 次，玩家讀規則時看到的是前者。</t>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>元素形態×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「元素形態」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -3255,14 +3563,19 @@
 迷信</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>「迷信」是「神秘迷信」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>迷信×14</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>迷信</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「迷信（Superstition）」14 次。</t>
         </is>
       </c>
     </row>
@@ -3301,14 +3614,19 @@
 遁術</t>
         </is>
       </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>「遁術」是「天遁術」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>遁術×4</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>遁術</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「遁術（Abundant Step）」4 次。</t>
         </is>
       </c>
     </row>
@@ -3347,14 +3665,19 @@
 高級魔法</t>
         </is>
       </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>高級魔法×22</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>高級魔法</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「高級魔法（Major Magic）」22 次。</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3716,19 @@
 次級魔法</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>次級魔法×40</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>次級魔法</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「次級魔法（Minor Magic）」40 次。</t>
         </is>
       </c>
     </row>
@@ -3439,14 +3767,20 @@
 狂獸騎士團</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>狂獸騎士團×6
+獸之騎士團×3</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>狂獸騎士團</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「狂獸騎士團（Order of the Beast）」6 次。</t>
         </is>
       </c>
     </row>
@@ -3485,14 +3819,20 @@
 韌性</t>
         </is>
       </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>韌性×6
+堅韌身軀×2</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>韌性</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「韌性（Resiliency）」6 次。</t>
         </is>
       </c>
     </row>
@@ -3531,12 +3871,17 @@
 酸鏢</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr">
         <is>
           <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
@@ -3577,14 +3922,19 @@
 威嚇怒視</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>威嚇凝視×18</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>威嚇凝視</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「威嚇凝視（Intimidating Glare）」18 次。</t>
         </is>
       </c>
     </row>
@@ -3623,14 +3973,19 @@
 煙霧炸彈</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>煙霧彈×3（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「煙霧彈」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -3669,14 +4024,19 @@
 防衛戰姿</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>守衛姿態×10</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>守衛姿態</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「守衛姿態（Guarded Stance）」10 次。</t>
         </is>
       </c>
     </row>
@@ -3715,14 +4075,19 @@
 怖懼狂嚎</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>怖懼狂嚎×10</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>怖懼狂嚎</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
         </is>
       </c>
     </row>
@@ -3761,14 +4126,19 @@
 野性之怒</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>野性之怒×28</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>野性之怒</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「野性之怒（Animal Fury）」28 次。</t>
         </is>
       </c>
     </row>
@@ -3807,14 +4177,19 @@
 絕望靈光</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>絕望靈氳（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>CHM 寫「絕望靈氳」，兩種現有寫法都不是；系統介面 v0.1.4 也已把 aura 統一成「靈氳」，可以考慮跟上。</t>
         </is>
       </c>
     </row>
@@ -3853,14 +4228,19 @@
 吉祥烙記</t>
         </is>
       </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>吉祥烙記×2</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>吉祥烙記</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「吉祥烙記（Auspicious Mark）」2 次。</t>
         </is>
       </c>
     </row>
@@ -3899,14 +4279,19 @@
 致命精確</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>致命精確×4</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>致命精確</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「致命精確（Deadly Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -3945,14 +4330,19 @@
 輕身縱</t>
         </is>
       </c>
-      <c r="H72" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>輕功×2</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>輕功</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「輕功（High Jump）」2 次。</t>
         </is>
       </c>
     </row>
@@ -3991,12 +4381,18 @@
 毒性抗力</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>毒性抗力×6
+毒素抗力×4</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="J73" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -4037,12 +4433,17 @@
 眩目之觸</t>
         </is>
       </c>
-      <c r="H74" s="13" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr">
+      <c r="J74" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -4083,14 +4484,19 @@
 撼地一擊</t>
         </is>
       </c>
-      <c r="H75" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>大地之擊×2</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>大地之擊</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「大地之擊（Ground Breaker）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4129,14 +4535,20 @@
 技藝精湛</t>
         </is>
       </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>技能專精×40
+技藝精湛×4</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>技能專精</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「技能專精（Skill Mastery）」40 次。</t>
         </is>
       </c>
     </row>
@@ -4175,14 +4587,20 @@
 迅足</t>
         </is>
       </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>迅足×8
+快步×4（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>迅足</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「迅足（Swift Foot）」8 次。</t>
         </is>
       </c>
     </row>
@@ -4221,14 +4639,19 @@
 逸聞知識</t>
         </is>
       </c>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>逸聞知識×4</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>逸聞知識</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「逸聞知識（Bardic Knowledge）」4 次。</t>
         </is>
       </c>
     </row>
@@ -4267,14 +4690,19 @@
 流血猛擊</t>
         </is>
       </c>
-      <c r="H79" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>流血猛擊×4</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>流血猛擊</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「流血猛擊（Bleeding Blow）」4 次。</t>
         </is>
       </c>
     </row>
@@ -4313,14 +4741,19 @@
 致殘猛擊</t>
         </is>
       </c>
-      <c r="H80" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>致殘猛擊×2</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>致殘猛擊</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「致殘猛擊（Crippling Blow）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4359,14 +4792,19 @@
 吞噬魔法</t>
         </is>
       </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>吞噬魔法×6</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>吞噬魔法</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「吞噬魔法（Eater of Magic）」6 次。</t>
         </is>
       </c>
     </row>
@@ -4405,14 +4843,19 @@
 毒性持續</t>
         </is>
       </c>
-      <c r="H82" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>毒性持續×2</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>毒性持續</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「毒性持續（Lasting Poison）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4451,14 +4894,20 @@
 飛簷走壁</t>
         </is>
       </c>
-      <c r="H83" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>飛簷走壁×2
+和靈動攀爬×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>飛簷走壁</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「飛簷走壁（Nimble Climber）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4497,14 +4946,19 @@
 狂暴跳躍</t>
         </is>
       </c>
-      <c r="H84" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>狂暴跳躍×14</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>狂暴跳躍</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「狂暴跳躍（Raging Leaper）」14 次。</t>
         </is>
       </c>
     </row>
@@ -4543,14 +4997,19 @@
 狂暴遊者</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>狂暴遊者×10</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>狂暴遊者</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「狂暴遊者（Raging Swimmer）」10 次。</t>
         </is>
       </c>
     </row>
@@ -4589,14 +5048,19 @@
 敏銳精確</t>
         </is>
       </c>
-      <c r="H86" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>敏銳精確×2</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>敏銳精確</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「敏銳精確（Sharpened Accuracy）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4635,14 +5099,19 @@
 奮勇衝刺</t>
         </is>
       </c>
-      <c r="H87" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>奮力衝刺×6</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>奮力衝刺</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「奮力衝刺（Sprint）」6 次。</t>
         </is>
       </c>
     </row>
@@ -4681,12 +5150,17 @@
 電瞬步</t>
         </is>
       </c>
-      <c r="H88" s="13" t="inlineStr">
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr">
+      <c r="J88" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -4727,14 +5201,19 @@
 詭擊</t>
         </is>
       </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>詭擊×6</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>詭擊</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「詭擊（Unexpected Strike）」6 次。</t>
         </is>
       </c>
     </row>
@@ -4773,14 +5252,19 @@
 獵巫人</t>
         </is>
       </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>獵巫人×8</t>
+        </is>
+      </c>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>獵巫人</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「獵巫人（Witch Hunter）」8 次。</t>
         </is>
       </c>
     </row>
@@ -4819,12 +5303,17 @@
 異怪形態</t>
         </is>
       </c>
-      <c r="H91" s="13" t="inlineStr">
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I91" s="11" t="inlineStr">
+      <c r="J91" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -4865,14 +5354,19 @@
 意識鑽探</t>
         </is>
       </c>
-      <c r="H92" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>意識鑽刺×2</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
+        <is>
+          <t>意識鑽刺</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「意識鑽刺（Brain Drain）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4911,14 +5405,19 @@
 心若明鏡</t>
         </is>
       </c>
-      <c r="H93" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>心如堅鋼×10</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>心如堅鋼</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「心如堅鋼（Clear Mind）」10 次。</t>
         </is>
       </c>
     </row>
@@ -4957,14 +5456,19 @@
 無畏狂暴</t>
         </is>
       </c>
-      <c r="H94" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>無懼狂暴×6</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>無懼狂暴</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「無懼狂暴（Fearless Rage）」6 次。</t>
         </is>
       </c>
     </row>
@@ -5003,14 +5507,19 @@
 皮外小傷</t>
         </is>
       </c>
-      <c r="H95" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>不屈武勇×4</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>不屈武勇</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「不屈武勇（Flesh Wound）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5049,14 +5558,19 @@
 高等狩獵目標</t>
         </is>
       </c>
-      <c r="H96" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>高等狩獵目標×4</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>高等狩獵目標</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5095,14 +5609,19 @@
 狂怒激發</t>
         </is>
       </c>
-      <c r="H97" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>狂怒激發×2</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>狂怒激發</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5141,14 +5660,19 @@
 致死精確</t>
         </is>
       </c>
-      <c r="H98" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H98" s="11" t="inlineStr">
+        <is>
+          <t>致死精確×4</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>致死精確</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「致死精確（Lethal Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5711,17 @@
 生命視野</t>
         </is>
       </c>
-      <c r="H99" s="13" t="inlineStr">
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -5233,12 +5762,17 @@
 輕身步</t>
         </is>
       </c>
-      <c r="H100" s="13" t="inlineStr">
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr">
+      <c r="J100" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -5279,14 +5813,19 @@
 超速反射</t>
         </is>
       </c>
-      <c r="H101" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>超速反射×8</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>超速反射</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「超速反射（Quick Reflexes）」8 次。</t>
         </is>
       </c>
     </row>
@@ -5325,14 +5864,19 @@
 激發怒意</t>
         </is>
       </c>
-      <c r="H102" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>無邊怒火×10</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>無邊怒火</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「無邊怒火（Roused Anger）」10 次。</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5915,17 @@
 遲緩一擊</t>
         </is>
       </c>
-      <c r="H103" s="13" t="inlineStr">
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr">
+      <c r="J103" s="11" t="inlineStr">
         <is>
           <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
@@ -5417,14 +5966,20 @@
 野蠻破壞</t>
         </is>
       </c>
-      <c r="H104" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>破壞者×4
+粉碎者×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>破壞者</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「破壞者（Smasher）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5462,12 +6017,17 @@
           <t>文本×384</t>
         </is>
       </c>
-      <c r="H105" s="13" t="inlineStr">
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I105" s="11" t="inlineStr">
+      <c r="J105" s="11" t="inlineStr">
         <is>
           <t>合集包多是法術欄位的「見文本」（see text），系統介面是「文本頁」；台灣一般說「內文」，但倉庫裡還沒有現成寫法。</t>
         </is>
@@ -5507,12 +6067,17 @@
           <t>信息×211</t>
         </is>
       </c>
-      <c r="H106" s="12" t="inlineStr">
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
         <is>
           <t>訊息</t>
         </is>
       </c>
-      <c r="I106" s="11" t="inlineStr">
+      <c r="J106" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「訊息」，mods、compendium 已經這樣用。</t>
         </is>
@@ -5552,12 +6117,17 @@
           <t>激活×59</t>
         </is>
       </c>
-      <c r="H107" s="12" t="inlineStr">
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
         <is>
           <t>啟動</t>
         </is>
       </c>
-      <c r="I107" s="11" t="inlineStr">
+      <c r="J107" s="11" t="inlineStr">
         <is>
           <t>全是合集包內文的「激活某能力」；合集包已有 197 處寫「啟動」。</t>
         </is>
@@ -5597,12 +6167,17 @@
           <t>圖標×3</t>
         </is>
       </c>
-      <c r="H108" s="12" t="inlineStr">
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
         <is>
           <t>圖示</t>
         </is>
       </c>
-      <c r="I108" s="11" t="inlineStr">
+      <c r="J108" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「圖示」，mods 已經這樣用。</t>
         </is>
@@ -5642,12 +6217,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H109" s="12" t="inlineStr">
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
         <is>
           <t>設定</t>
         </is>
       </c>
-      <c r="I109" s="11" t="inlineStr">
+      <c r="J109" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「設定」，mods、compendium 已經這樣用。</t>
         </is>
@@ -5687,12 +6267,17 @@
           <t>添加×29</t>
         </is>
       </c>
-      <c r="H110" s="13" t="inlineStr">
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr">
+      <c r="J110" s="11" t="inlineStr">
         <is>
           <t>這些是規則內文的「添加到加值上」，改不改看語氣；介面上的「添加」早就統一成「新增」了。</t>
         </is>
@@ -5732,12 +6317,17 @@
           <t>复×27</t>
         </is>
       </c>
-      <c r="H111" s="12" t="inlineStr">
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
         <is>
           <t>復</t>
         </is>
       </c>
-      <c r="I111" s="11" t="inlineStr">
+      <c r="J111" s="11" t="inlineStr">
         <is>
           <t>「复」是簡體字，同一個詞在倉庫其他地方已經寫成「復」。</t>
         </is>
@@ -5777,12 +6367,17 @@
           <t>數據×23</t>
         </is>
       </c>
-      <c r="H112" s="12" t="inlineStr">
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="I112" s="11" t="inlineStr">
+      <c r="J112" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「資料」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -5822,12 +6417,17 @@
           <t>鏈接×25</t>
         </is>
       </c>
-      <c r="H113" s="12" t="inlineStr">
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="12" t="inlineStr">
         <is>
           <t>連結</t>
         </is>
       </c>
-      <c r="I113" s="11" t="inlineStr">
+      <c r="J113" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「連結」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -5867,12 +6467,17 @@
           <t>質量×24</t>
         </is>
       </c>
-      <c r="H114" s="12" t="inlineStr">
+      <c r="H114" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
         <is>
           <t>品質</t>
         </is>
       </c>
-      <c r="I114" s="11" t="inlineStr">
+      <c r="J114" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「品質」，compendium 已經這樣用。</t>
         </is>
@@ -5912,12 +6517,17 @@
           <t>界面×2</t>
         </is>
       </c>
-      <c r="H115" s="13" t="inlineStr">
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I115" s="11" t="inlineStr">
+      <c r="J115" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「介面」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -5957,12 +6567,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H116" s="12" t="inlineStr">
+      <c r="H116" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
         <is>
           <t>拖曳</t>
         </is>
       </c>
-      <c r="I116" s="11" t="inlineStr">
+      <c r="J116" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「拖曳」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -6002,12 +6617,17 @@
           <t>變量×7</t>
         </is>
       </c>
-      <c r="H117" s="12" t="inlineStr">
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
         <is>
           <t>變數</t>
         </is>
       </c>
-      <c r="I117" s="11" t="inlineStr">
+      <c r="J117" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「變數」，compendium 已經這樣用。</t>
         </is>
@@ -6047,12 +6667,17 @@
           <t>窗口×8</t>
         </is>
       </c>
-      <c r="H118" s="13" t="inlineStr">
+      <c r="H118" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I118" s="11" t="inlineStr">
+      <c r="J118" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「視窗」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6092,12 +6717,17 @@
           <t>自定義×1</t>
         </is>
       </c>
-      <c r="H119" s="12" t="inlineStr">
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
         <is>
           <t>自訂</t>
         </is>
       </c>
-      <c r="I119" s="11" t="inlineStr">
+      <c r="J119" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「自訂」，mods、compendium 已經這樣用。</t>
         </is>
@@ -6137,12 +6767,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H120" s="12" t="inlineStr">
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
         <is>
           <t>全域</t>
         </is>
       </c>
-      <c r="I120" s="11" t="inlineStr">
+      <c r="J120" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「全域」，mods、compendium 已經這樣用。</t>
         </is>
@@ -6182,12 +6817,17 @@
           <t>創建×14</t>
         </is>
       </c>
-      <c r="H121" s="12" t="inlineStr">
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
         <is>
           <t>建立</t>
         </is>
       </c>
-      <c r="I121" s="11" t="inlineStr">
+      <c r="J121" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「建立」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -6227,12 +6867,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H122" s="12" t="inlineStr">
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
         <is>
           <t>使用者</t>
         </is>
       </c>
-      <c r="I122" s="11" t="inlineStr">
+      <c r="J122" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「使用者」，mods、compendium 已經這樣用。</t>
         </is>
@@ -6272,12 +6917,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H123" s="13" t="inlineStr">
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I123" s="11" t="inlineStr">
+      <c r="J123" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「偵錯」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6317,12 +6967,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H124" s="13" t="inlineStr">
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I124" s="11" t="inlineStr">
+      <c r="J124" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「控制項」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6362,12 +7017,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr">
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
         <is>
           <t>執行</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="J125" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「執行」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -6407,12 +7067,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H126" s="12" t="inlineStr">
+      <c r="H126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
         <is>
           <t>指示物</t>
         </is>
       </c>
-      <c r="I126" s="11" t="inlineStr">
+      <c r="J126" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「指示物」，pf1-zhtw、mods 已經這樣用。</t>
         </is>
@@ -6452,12 +7117,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="12" t="inlineStr">
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="I127" s="11" t="inlineStr">
+      <c r="J127" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「欄位」，pf1-zhtw、compendium 已經這樣用。</t>
         </is>
@@ -6497,12 +7167,17 @@
           <t>默認×4</t>
         </is>
       </c>
-      <c r="H128" s="12" t="inlineStr">
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
         <is>
           <t>預設</t>
         </is>
       </c>
-      <c r="I128" s="11" t="inlineStr">
+      <c r="J128" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「預設」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
@@ -6542,12 +7217,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H129" s="12" t="inlineStr">
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
         <is>
           <t>搜尋</t>
         </is>
       </c>
-      <c r="I129" s="11" t="inlineStr">
+      <c r="J129" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「搜尋」，mods、compendium 已經這樣用。</t>
         </is>
@@ -6587,12 +7267,17 @@
           <t>兼容×1</t>
         </is>
       </c>
-      <c r="H130" s="12" t="inlineStr">
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
         <is>
           <t>相容</t>
         </is>
       </c>
-      <c r="I130" s="11" t="inlineStr">
+      <c r="J130" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「相容」，mods 已經這樣用。</t>
         </is>
@@ -6632,12 +7317,17 @@
           <t>代碼×1</t>
         </is>
       </c>
-      <c r="H131" s="13" t="inlineStr">
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I131" s="11" t="inlineStr">
+      <c r="J131" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「程式碼」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6677,12 +7367,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H132" s="13" t="inlineStr">
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I132" s="11" t="inlineStr">
+      <c r="J132" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「批次」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6722,12 +7417,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H133" s="13" t="inlineStr">
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I133" s="11" t="inlineStr">
+      <c r="J133" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「攝影機」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6767,12 +7467,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H134" s="12" t="inlineStr">
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
         <is>
           <t>貼上</t>
         </is>
       </c>
-      <c r="I134" s="11" t="inlineStr">
+      <c r="J134" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「貼上」，mods、compendium 已經這樣用。</t>
         </is>
@@ -6812,12 +7517,17 @@
           <t>刷新×2</t>
         </is>
       </c>
-      <c r="H135" s="13" t="inlineStr">
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I135" s="11" t="inlineStr">
+      <c r="J135" s="11" t="inlineStr">
         <is>
           <t>這裡是「刷新持續時間」（重新計時），介面用的「重新整理」不適用，需要人看語境。</t>
         </is>
@@ -6857,12 +7567,17 @@
           <t>钟×2</t>
         </is>
       </c>
-      <c r="H136" s="12" t="inlineStr">
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="12" t="inlineStr">
         <is>
           <t>鐘</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr">
+      <c r="J136" s="11" t="inlineStr">
         <is>
           <t>「钟」是簡體字，同一個詞在倉庫其他地方已經寫成「鐘」。</t>
         </is>
@@ -6902,12 +7617,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H137" s="12" t="inlineStr">
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
         <is>
           <t>匯入</t>
         </is>
       </c>
-      <c r="I137" s="11" t="inlineStr">
+      <c r="J137" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「匯入」，mods 已經這樣用。</t>
         </is>
@@ -6947,12 +7667,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H138" s="13" t="inlineStr">
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I138" s="11" t="inlineStr">
+      <c r="J138" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「伺服器」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -6992,12 +7717,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H139" s="13" t="inlineStr">
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
         <is>
           <t>待裁定</t>
         </is>
       </c>
-      <c r="I139" s="11" t="inlineStr">
+      <c r="J139" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣一般寫「游標」，但三個倉庫都還沒有這個寫法可對照。</t>
         </is>
@@ -7037,19 +7767,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H140" s="12" t="inlineStr">
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr">
         <is>
           <t>音訊</t>
         </is>
       </c>
-      <c r="I140" s="11" t="inlineStr">
+      <c r="J140" s="11" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「音訊」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I140"/>
+  <autoFilter ref="A1:J140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7153,7 +7888,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>「奖励专长」用了 5 次，另一種只有 1 次，照多數。</t>
+          <t>跟繁體版同一條，繁體版建議「獎勵專長」：CHM v2.33.0 寫「獎勵專長（Bonus Feats）」89 次。</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7930,7 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>「气池」用了 3 次，另一種只有 1 次，照多數。</t>
+          <t>跟繁體版同一條，繁體版建議「氣池」：CHM v2.33.0 寫「氣池（Ki Pool）」8 次。</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7972,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>「忍法·心技体」是忍者版刻意取的風格名，但通用的 Feat 就叫「专长」。</t>
+          <t>跟繁體版同一條，繁體版建議「專長」：CHM v2.33.0 寫「專長（Feat）」172 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -7274,14 +8009,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>盗贼天赋</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>職業名 Rogue 譯作「游荡者」，但內文多寫「盗贼天赋」，兩邊打架；沒標職業的通用條目被譯成忍者風格的「忍法·身合」，看起來是誤植。</t>
+          <t>跟繁體版同一條，繁體版建議「盜賊天賦」：CHM v2.33.0 寫「盜賊天賦（Rogue Talent）」29 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -7323,7 +8058,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「自发施法」29 次，「法术转换」只有 6 次。</t>
+          <t>跟繁體版同一條，繁體版建議「自發施法」：CHM v2.33.0 寫「自發施法（Spontaneous Casting）」16 次。</t>
         </is>
       </c>
     </row>
@@ -7365,7 +8100,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -7400,14 +8135,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>徒手打击</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>兩種說法各有人用；內文「徒手打击」276 次、「徒手击打」140 次，差距不夠大。</t>
+          <t>跟繁體版同一條，繁體版建議「徒手打擊」：CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
         </is>
       </c>
     </row>
@@ -7442,14 +8177,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>增强伤害减免</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>「伤害减免」是「增强伤害减免」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「增強傷害減免」：CHM v2.33.0 寫「增強傷害減免（Increased Damage Reduction）」20 次。</t>
         </is>
       </c>
     </row>
@@ -7491,7 +8226,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「引导能量」179 次，「能量引导」只有 3 次。</t>
+          <t>跟繁體版同一條，繁體版建議「引導能量」：CHM 內文寫「引導能量」759 次、「能量引導」40 次。</t>
         </is>
       </c>
     </row>
@@ -7533,7 +8268,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「昏暗视觉」158 次，「低光视力」只有 1 次。</t>
+          <t>跟繁體版同一條，繁體版建議「昏暗視覺」：CHM v2.33.0 寫「昏暗視覺（Low-Light Vision）」102 次。</t>
         </is>
       </c>
     </row>
@@ -7575,7 +8310,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「喷吐武器」102 次，「喷吐龙息」只有 0 次。</t>
+          <t>跟繁體版同一條，繁體版建議「噴吐武器」：CHM v2.33.0 寫「噴吐武器（Breath Weapon）」6 次。</t>
         </is>
       </c>
     </row>
@@ -7617,7 +8352,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>「翅膀」是一般用字，內文次數不能當證據；龍族血統版叫「龙翼」可能是刻意區分，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -7652,14 +8387,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>反射闪避</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「反射閃避」：CHM v2.33.0 寫「反射閃避（Evasion）」20 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -7701,7 +8436,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「击飞」27 次，「一击即飞」只有 0 次。</t>
+          <t>跟繁體版同一條，繁體版建議「擊飛」：CHM v2.33.0 寫「擊飛（Knockback）」8 次。</t>
         </is>
       </c>
     </row>
@@ -7736,14 +8471,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>迷信</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>「迷信」是「神秘迷信」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「迷信」：CHM v2.33.0 寫「迷信（Superstition）」14 次。</t>
         </is>
       </c>
     </row>
@@ -7778,14 +8513,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>元素身躯</t>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>簡體版內文寫「元素身躯」12 次，「元素之躯」只有 0 次。</t>
+          <t>繁體版同一條也是待裁定：CHM 寫「元素形態」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -7820,14 +8555,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>遁术</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>「遁术」是「天遁术」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「遁術」：CHM v2.33.0 寫「遁術（Abundant Step）」4 次。</t>
         </is>
       </c>
     </row>
@@ -7862,14 +8597,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>高级魔法</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「高級魔法」：CHM v2.33.0 寫「高級魔法（Major Magic）」22 次。</t>
         </is>
       </c>
     </row>
@@ -7911,7 +8646,7 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>「酸镖」是「强酸镖」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -7946,14 +8681,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>次级魔法</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「次級魔法」：CHM v2.33.0 寫「次級魔法（Minor Magic）」40 次。</t>
         </is>
       </c>
     </row>
@@ -7988,14 +8723,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>狂兽骑士团</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「狂獸騎士團」：CHM v2.33.0 寫「狂獸騎士團（Order of the Beast）」6 次。</t>
         </is>
       </c>
     </row>
@@ -8030,14 +8765,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>韧性</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「韌性」：CHM v2.33.0 寫「韌性（Resiliency）」6 次。</t>
         </is>
       </c>
     </row>
@@ -8072,14 +8807,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>威吓凝视</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「威嚇凝視」：CHM v2.33.0 寫「威嚇凝視（Intimidating Glare）」18 次。</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8856,7 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>忍者職業的版本刻意改成「忍法·」風格的名字，要不要跟一般版本統一，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：CHM 寫「煙霧彈」，三個倉庫都沒用這個寫法；需要人來決定要不要改成 CHM 的說法。</t>
         </is>
       </c>
     </row>
@@ -8156,14 +8891,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>守卫姿态</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「守衛姿態」：CHM v2.33.0 寫「守衛姿態（Guarded Stance）」10 次。</t>
         </is>
       </c>
     </row>
@@ -8198,14 +8933,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>怖惧狂嚎</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「怖懼狂嚎」：CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
         </is>
       </c>
     </row>
@@ -8240,14 +8975,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>野性之怒</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「野性之怒」：CHM v2.33.0 寫「野性之怒（Animal Fury）」28 次。</t>
         </is>
       </c>
     </row>
@@ -8289,7 +9024,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：CHM 寫「絕望靈氳」，兩種現有寫法都不是；系統介面 v0.1.4 也已把 aura 統一成「靈氳」，可以考慮跟上。</t>
         </is>
       </c>
     </row>
@@ -8324,14 +9059,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>吉祥烙记</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「吉祥烙記」：CHM v2.33.0 寫「吉祥烙記（Auspicious Mark）」2 次。</t>
         </is>
       </c>
     </row>
@@ -8366,14 +9101,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>致命精确</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「致命精確」：CHM v2.33.0 寫「致命精確（Deadly Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -8408,14 +9143,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>轻功</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「輕功」：CHM v2.33.0 寫「輕功（High Jump）」2 次。</t>
         </is>
       </c>
     </row>
@@ -8457,7 +9192,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -8499,7 +9234,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -8534,14 +9269,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>大地之击</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「大地之擊」：CHM v2.33.0 寫「大地之擊（Ground Breaker）」2 次。</t>
         </is>
       </c>
     </row>
@@ -8576,14 +9311,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>技能专精</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「技能專精」：CHM v2.33.0 寫「技能專精（Skill Mastery）」40 次。</t>
         </is>
       </c>
     </row>
@@ -8618,14 +9353,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>迅足</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「迅足」：CHM v2.33.0 寫「迅足（Swift Foot）」8 次。</t>
         </is>
       </c>
     </row>
@@ -8660,14 +9395,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>逸闻知识</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「逸聞知識」：CHM v2.33.0 寫「逸聞知識（Bardic Knowledge）」4 次。</t>
         </is>
       </c>
     </row>
@@ -8702,14 +9437,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>流血猛击</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「流血猛擊」：CHM v2.33.0 寫「流血猛擊（Bleeding Blow）」4 次。</t>
         </is>
       </c>
     </row>
@@ -8744,14 +9479,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>致残猛击</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「致殘猛擊」：CHM v2.33.0 寫「致殘猛擊（Crippling Blow）」2 次。</t>
         </is>
       </c>
     </row>
@@ -8786,14 +9521,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>吞噬魔法</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「吞噬魔法」：CHM v2.33.0 寫「吞噬魔法（Eater of Magic）」6 次。</t>
         </is>
       </c>
     </row>
@@ -8828,14 +9563,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>毒性持续</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「毒性持續」：CHM v2.33.0 寫「毒性持續（Lasting Poison）」2 次。</t>
         </is>
       </c>
     </row>
@@ -8912,14 +9647,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>狂暴跳跃</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「狂暴跳躍」：CHM v2.33.0 寫「狂暴跳躍（Raging Leaper）」14 次。</t>
         </is>
       </c>
     </row>
@@ -8954,14 +9689,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>狂暴游者</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「狂暴遊者」：CHM v2.33.0 寫「狂暴遊者（Raging Swimmer）」10 次。</t>
         </is>
       </c>
     </row>
@@ -8996,14 +9731,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>敏锐精确</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「敏銳精確」：CHM v2.33.0 寫「敏銳精確（Sharpened Accuracy）」2 次。</t>
         </is>
       </c>
     </row>
@@ -9038,14 +9773,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>奋力冲刺</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「奮力衝刺」：CHM v2.33.0 寫「奮力衝刺（Sprint）」6 次。</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9822,7 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -9122,14 +9857,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>诡击</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「詭擊」：CHM v2.33.0 寫「詭擊（Unexpected Strike）」6 次。</t>
         </is>
       </c>
     </row>
@@ -9164,14 +9899,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>猎巫人</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「獵巫人」：CHM v2.33.0 寫「獵巫人（Witch Hunter）」8 次。</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9948,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -9248,14 +9983,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>意识钻刺</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「意識鑽刺」：CHM v2.33.0 寫「意識鑽刺（Brain Drain）」2 次。</t>
         </is>
       </c>
     </row>
@@ -9290,14 +10025,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>心如坚钢</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「心如堅鋼」：CHM v2.33.0 寫「心如堅鋼（Clear Mind）」10 次。</t>
         </is>
       </c>
     </row>
@@ -9332,14 +10067,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>无惧狂暴</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「無懼狂暴」：CHM v2.33.0 寫「無懼狂暴（Fearless Rage）」6 次。</t>
         </is>
       </c>
     </row>
@@ -9374,14 +10109,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>不屈武勇</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「不屈武勇」：CHM v2.33.0 寫「不屈武勇（Flesh Wound）」4 次。</t>
         </is>
       </c>
     </row>
@@ -9416,14 +10151,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>高等狩猎目标</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「高等狩獵目標」：CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
         </is>
       </c>
     </row>
@@ -9458,14 +10193,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>狂怒激发</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「狂怒激發」：CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
         </is>
       </c>
     </row>
@@ -9500,14 +10235,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>致死精确</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「致死精確」：CHM v2.33.0 寫「致死精確（Lethal Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -9549,7 +10284,7 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -9591,7 +10326,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -9626,14 +10361,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>超速反射</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「超速反射」：CHM v2.33.0 寫「超速反射（Quick Reflexes）」8 次。</t>
         </is>
       </c>
     </row>
@@ -9668,14 +10403,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>无边怒火</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「無邊怒火」：CHM v2.33.0 寫「無邊怒火（Roused Anger）」10 次。</t>
         </is>
       </c>
     </row>
@@ -9717,7 +10452,7 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -9752,14 +10487,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>破坏者</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「破壞者」：CHM v2.33.0 寫「破壞者（Smasher）」4 次。</t>
         </is>
       </c>
     </row>

--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="簡體合集包" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$J$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'繁體三倉'!$A$1:$J$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'簡體合集包'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>系統介面、模組、合集包（繁體）三個倉庫一起比，共 139 條。玩家最常看到的排在最上面。</t>
+          <t>系統介面、模組、合集包（繁體）三個倉庫一起比，共 142 條。玩家最常看到的排在最上面。</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>已裁定（26 條）。維護者 2026-10-17 回覆決定的譯名。</t>
+          <t>已裁定（32 條）。維護者 2026-10-17 回覆決定的譯名。</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>有建議譯名（101 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
+          <t>有建議譯名（100 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>待裁定（12 條）。拿不準，需要人來決定。</t>
+          <t>待裁定（10 條）。拿不準，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1168,200 +1168,201 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 不同</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 新定名不同</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>絆摔</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>絆摔×19</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>絆摔×93
+摔絆×217</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>摔絆（v2.28.5 全書統一）</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>摔絆</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>已裁定，照 CHM（v2.28.5「絆摔→摔絆」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Fast Healing</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 不同</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 新定名不同</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>快速醫療</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>快速治療</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>快速治療×16
+快速痊癒×4</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>快速治療（v2.28.5 全書統一）</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>快速治療</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>已裁定，照 CHM（「快速痊癒→快速治療」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Acid（傷害類型）</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 不同</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>與 CHM 新定名不同</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>強酸</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>酸蝕（v2.28.5 全書統一）</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>酸蝕</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>已裁定，照 CHM。只改傷害類型、能量類型、抗力；強酸箭、強酸炸彈、強酸瓶這類法術與物品名不動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
           <t>Finesse</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>武器／護甲</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>跨倉＋倉內不一致</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>靈巧</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>嫻熟
 強制嫻熟
 嫻熟目標</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>靈巧×8</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>靈巧</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>CHM v2.33.0 寫「靈巧（Finesse）」8 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Sunder</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>武器／護甲</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>跨倉不一致</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>破損</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>破武</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>擊破×10（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>擊破</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>已裁定，跟 CHM 一致（CHM v2.28.5 已把「破武」統一成「擊破」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Armor Focus</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>專長名</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>跨倉不一致</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>護甲專攻×3</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>盔甲專攻</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>護甲專攻</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>「護甲專攻」用了 3 次，另一種只有 1 次，照多數。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Gang Up</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>專長名</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>一擁而上×2
-聯手</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>一擁而上</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>一擁而上×4</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>一擁而上</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>CHM v2.33.0 寫「一擁而上（Gang Up）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1371,48 +1372,47 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Furious Focus</t>
+          <t>Sunder</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>專長名</t>
+          <t>武器／護甲</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>跨倉＋倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>破損</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>沉著暴怒×2
-猛力專攻</t>
+          <t>破武</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>沉著暴怒</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>沉著暴怒×4</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>沉著暴怒</t>
+          <t>擊破×10（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>擊破</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「沉著暴怒（Furious Focus）」4 次。</t>
+          <t>已裁定，跟 CHM 一致（CHM v2.28.5 已把「破武」統一成「擊破」）。</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Outflank</t>
+          <t>Armor Focus</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>跨倉＋倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1442,28 +1442,27 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>包抄×2
-側面包抄</t>
+          <t>護甲專攻×3</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>包抄</t>
+          <t>盔甲專攻</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>包抄×8</t>
+          <t>沒有附英文的定名</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>包抄</t>
+          <t>護甲專攻</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「包抄（Outflank）」8 次。</t>
+          <t>「護甲專攻」用了 3 次，另一種只有 1 次，照多數。</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1472,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Snake Sidewind</t>
+          <t>Gang Up</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -1493,28 +1492,28 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>蛇形步×2
-蛇行</t>
+          <t>一擁而上×2
+聯手</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>蛇行</t>
+          <t>一擁而上</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>蛇行×4</t>
+          <t>一擁而上×4</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>蛇行</t>
+          <t>一擁而上</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「蛇行（Snake Sidewind）」4 次。</t>
+          <t>CHM v2.33.0 寫「一擁而上（Gang Up）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1523,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Martial Focus</t>
+          <t>Furious Focus</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -1544,28 +1543,28 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>武器專家×2
-武術專攻</t>
+          <t>沉著暴怒×2
+猛力專攻</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>武器專家</t>
+          <t>沉著暴怒</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>武術專精×2（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>武術專精</t>
+          <t>沉著暴怒×4</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>沉著暴怒</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>已裁定，跟 CHM 一致。</t>
+          <t>CHM v2.33.0 寫「沉著暴怒（Furious Focus）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1574,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Focused Inspiration</t>
+          <t>Outflank</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1595,28 +1594,28 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>專注靈感
-靈感專注</t>
+          <t>包抄×2
+側面包抄</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>靈感專注</t>
+          <t>包抄</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
+          <t>包抄×8</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>靈感專注</t>
+          <t>包抄</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>2 個倉庫都用「靈感專注」，只有 mods 另有寫法。</t>
+          <t>CHM v2.33.0 寫「包抄（Outflank）」8 次。</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1625,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Improved Armor Focus</t>
+          <t>Snake Sidewind</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1636,7 +1635,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>跨倉不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1646,27 +1645,28 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>精通護甲專攻</t>
+          <t>蛇形步×2
+蛇行</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>進階盔甲專攻</t>
+          <t>蛇行</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>精通護甲專攻</t>
+          <t>蛇行×4</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>蛇行</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>已裁定。</t>
+          <t>CHM v2.33.0 寫「蛇行（Snake Sidewind）」4 次。</t>
         </is>
       </c>
     </row>
@@ -1676,200 +1676,201 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
+          <t>Martial Focus</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>專長名</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>跨倉＋倉內不一致</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>武器專家×2
+武術專攻</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>武器專家</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>武術專精×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>武術專精</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>已裁定，跟 CHM 一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Focused Inspiration</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>專長名</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>跨倉＋倉內不一致</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>專注靈感
+靈感專注</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>靈感專注</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>靈感專注</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>2 個倉庫都用「靈感專注」，只有 mods 另有寫法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Improved Armor Focus</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>專長名</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>跨倉不一致</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>精通護甲專攻</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>進階盔甲專攻</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>精通護甲專攻</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>已裁定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
           <t>Ooze</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>種族／生物類型</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>跨倉不一致</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>泥怪</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>泥怪</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>泥形生物</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>泥怪×8
 泥形生物×2
 泥形怪物×4（倉庫沒用）</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>泥怪</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>CHM v2.33.0 寫「泥怪（Ooze）」8 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Monstrous Humanoid</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>種族／生物類型</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>跨倉不一致</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>類人怪物</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>類人怪物</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>人形怪物</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>人形怪物×7
-人型怪物×3（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>人形怪物</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>CHM v2.33.0 寫「人形怪物（Monstrous Humanoid）」7 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Kami</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>種族／生物類型</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>跨倉不一致</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>神靈</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>神</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>神靈×6</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>神靈</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>CHM v2.33.0 寫「神靈（Kami）」6 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Extraplanar</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>種族／生物類型</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>跨倉不一致</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>跨位面</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>異界</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>跨位面</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>已裁定。</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1880,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Wayang</t>
+          <t>Monstrous Humanoid</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -1894,33 +1895,33 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>皮影人</t>
+          <t>類人怪物</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>類人怪物</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>剪影人</t>
+          <t>人形怪物</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>剪影人×6
-剪影語×2（倉庫沒用）</t>
+          <t>人形怪物×7
+人型怪物×3（倉庫沒用）</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>剪影人</t>
+          <t>人形怪物</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「剪影人（Wayang）」6 次。</t>
+          <t>CHM v2.33.0 寫「人形怪物（Monstrous Humanoid）」7 次。</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1931,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Troop</t>
+          <t>Kami</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1945,12 +1946,12 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>部隊</t>
+          <t>神靈</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>軍隊</t>
+          <t>神</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -1960,17 +1961,17 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>部隊</t>
+          <t>神靈×6</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>神靈</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>已裁定。</t>
+          <t>CHM v2.33.0 寫「神靈（Kami）」6 次。</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1981,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Extraplanar</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1995,12 +1996,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>機體</t>
+          <t>跨位面</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>機器人</t>
+          <t>異界</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -2010,17 +2011,17 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>機器人×2</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>機器人</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>跨位面</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「機器人（Robot）」2 次。</t>
+          <t>已裁定。</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2031,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Leshy</t>
+          <t>Wayang</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -2045,32 +2046,33 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>萊西</t>
+          <t>皮影人</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>勒席</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>剪影人</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>萊西×2</t>
+          <t>剪影人×6
+剪影語×2（倉庫沒用）</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>萊西</t>
+          <t>剪影人</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「萊西（Leshy）」2 次。</t>
+          <t>CHM v2.33.0 寫「剪影人（Wayang）」6 次。</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2082,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Ratfolk</t>
+          <t>Troop</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -2095,33 +2097,32 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>鼠族</t>
+          <t>部隊</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>軍隊</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>鼠人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>鼠族×19
-鼠人×2</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>鼠族</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>部隊</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「鼠族（Ratfolk）」19 次。</t>
+          <t>已裁定。</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2132,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Azata</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -2146,12 +2147,12 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>靈使</t>
+          <t>機體</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>愛塔天族</t>
+          <t>機器人</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -2161,17 +2162,17 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>靈使×10</t>
+          <t>機器人×2</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>靈使</t>
+          <t>機器人</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「靈使（Azata）」10 次。</t>
+          <t>CHM v2.33.0 寫「機器人（Robot）」2 次。</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Archon</t>
+          <t>Leshy</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -2196,12 +2197,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>聖使</t>
+          <t>萊西</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>亞空天族</t>
+          <t>勒席</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -2211,18 +2212,17 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>聖使×2
-神使×9（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>萊西×2</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>萊西</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>待再確認：回覆選「神使」，但 CHM v2.28.5 的更新紀錄寫「亞空→聖使（Archon）」，是全書統一的定名；CHM 裡的「神使」集中在「神賜」頁，像是漏改。要「神使」還是「聖使」，請再確認。</t>
+          <t>CHM v2.33.0 寫「萊西（Leshy）」2 次。</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Agathion</t>
+          <t>Ratfolk</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -2247,32 +2247,33 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>衛使</t>
+          <t>鼠族</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>蓋丁天族</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>鼠人</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>福使×26（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>福使</t>
+          <t>鼠族×19
+鼠人×2</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>鼠族</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>已裁定，跟 CHM 一致。</t>
+          <t>CHM v2.33.0 寫「鼠族（Ratfolk）」19 次。</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2283,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Div</t>
+          <t>Azata</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -2297,12 +2298,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>妖靈</t>
+          <t>靈使</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>迪瓦</t>
+          <t>愛塔天族</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -2312,17 +2313,17 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>妖靈×22</t>
+          <t>靈使×10</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>妖靈</t>
+          <t>靈使</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「妖靈（Div）」22 次。</t>
+          <t>CHM v2.33.0 寫「靈使（Azata）」10 次。</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2333,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Derro</t>
+          <t>Archon</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -2347,12 +2348,12 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>迪洛人</t>
+          <t>聖使</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>迪洛矮人</t>
+          <t>亞空天族</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -2362,17 +2363,18 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>德洛人×2（倉庫沒用）</t>
+          <t>聖使×2
+神使×9（倉庫沒用）</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>德洛人</t>
+          <t>聖使</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>已裁定。CHM 寫「德洛人」13 次；另一個候選「癲儒」在 CHM 和三個倉庫都沒出現過，所以選「德洛人」。</t>
+          <t>已裁定，照 CHM（v2.28.5 全書統一「亞空→聖使」）。果園論壇要登入才能看，沒查到論壇用法。CHM「神賜」頁還有 9 處舊的「神使（archons）」，要回報 CHM 補改。</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2384,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Dark Folk</t>
+          <t>Agathion</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -2397,12 +2399,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>幽暗之民</t>
+          <t>衛使</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>暗黑民</t>
+          <t>蓋丁天族</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -2412,17 +2414,17 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
+          <t>福使×26（倉庫沒用）</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>幽暗之民</t>
+          <t>福使</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>已裁定。</t>
+          <t>已裁定，跟 CHM 一致。</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2434,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Demodand</t>
+          <t>Div</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -2447,12 +2449,12 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>神孽</t>
+          <t>妖靈</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>泰坦神孽</t>
+          <t>迪瓦</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -2462,17 +2464,17 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>魔孽×4（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>魔孽</t>
+          <t>妖靈×22</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>妖靈</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>已裁定，跟 CHM 一致。</t>
+          <t>CHM v2.33.0 寫「妖靈（Div）」22 次。</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2484,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Spawn of Rovagug</t>
+          <t>Derro</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
@@ -2497,12 +2499,12 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>拉瓦古格之嗣</t>
+          <t>迪洛人</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>拉瓦古格之子</t>
+          <t>迪洛矮人</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2512,17 +2514,17 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
+          <t>德洛人×2（倉庫沒用）</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>拉瓦古格之嗣</t>
+          <t>德洛人</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>已裁定。</t>
+          <t>已裁定。CHM 寫「德洛人」13 次；另一個候選「癲儒」在 CHM 和三個倉庫都沒出現過，所以選「德洛人」。</t>
         </is>
       </c>
     </row>
@@ -2532,48 +2534,47 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Bonus Feats</t>
+          <t>Dark Folk</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>幽暗之民</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>暗黑民</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>獎勵專長×5
-額外專長</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>獎勵專長×89</t>
-        </is>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>獎勵專長</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>幽暗之民</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「獎勵專長（Bonus Feats）」89 次。</t>
+          <t>已裁定。</t>
         </is>
       </c>
     </row>
@@ -2583,49 +2584,47 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Ki Pool</t>
+          <t>Demodand</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>神孽</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>泰坦神孽</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>氣池×3
-氣運丹田</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>氣池×8
-氣運丹田×2</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>氣池</t>
+          <t>魔孽×4（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>魔孽</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「氣池（Ki Pool）」8 次。</t>
+          <t>已裁定，跟 CHM 一致。</t>
         </is>
       </c>
     </row>
@@ -2635,48 +2634,47 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Feat</t>
+          <t>Spawn of Rovagug</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>職業能力名</t>
+          <t>種族／生物類型</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>拉瓦古格之嗣</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>拉瓦古格之子</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>專長×2
-忍法·心技體</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>專長×172</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>專長</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>拉瓦古格之嗣</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「專長（Feat）」172 次；CHM 裡找不到「忍法·」這種寫法。</t>
+          <t>已裁定。</t>
         </is>
       </c>
     </row>
@@ -2686,204 +2684,204 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
+          <t>Bonus Feats</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>獎勵專長×5
+額外專長</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>獎勵專長×89</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>獎勵專長</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「獎勵專長（Bonus Feats）」89 次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Ki Pool</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>氣池×3
+氣運丹田</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>氣池×8
+氣運丹田×2</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>氣池</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「氣池（Ki Pool）」8 次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Feat</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>倉內不一致</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>專長×2
+忍法·心技體</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>專長×172</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>專長</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>CHM v2.33.0 寫「專長（Feat）」172 次；CHM 裡找不到「忍法·」這種寫法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
           <t>Rogue Talent</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>職業能力名</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>倉內不一致</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>忍法·身合
 遊蕩者天賦
 盜賊天賦</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>盜賊天賦×29
 遊蕩者絕技×10（倉庫沒用）</t>
         </is>
       </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>盜賊天賦</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>CHM v2.33.0 寫「盜賊天賦（Rogue Talent）」29 次；CHM 裡找不到「忍法·」這種寫法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Spontaneous Casting</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>倉內不一致</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>自發施法×2
-法術轉換</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>自發施法×16
-法術轉換×2</t>
-        </is>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>自發施法</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>CHM v2.33.0 寫「自發施法（Spontaneous Casting）」16 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Amazing Inspiration</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>驚人靈感
-奇妙靈感</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>奇妙靈感</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>奇妙靈感×2</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>奇妙靈感</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>CHM v2.33.0 寫「奇妙靈感（Amazing Inspiration）」2 次。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>True Inspiration</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>職業能力名</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>跨倉＋倉內不一致</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>真實靈感
-靈感滿溢</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>靈感滿溢</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>靈感滿溢</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>2 個倉庫都用「靈感滿溢」，只有 mods 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2891,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Tenacious Inspiration</t>
+          <t>Spontaneous Casting</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -2903,7 +2901,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>跨倉＋倉內不一致</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
@@ -2913,28 +2911,29 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>頑強靈感
-執著靈感</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>執著靈感</t>
+          <t>自發施法×2
+法術轉換</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>執著靈感×2</t>
+          <t>自發施法×16
+法術轉換×2</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>執著靈感</t>
+          <t>自發施法</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「執著靈感（Tenacious Inspiration）」2 次。</t>
+          <t>CHM v2.33.0 寫「自發施法（Spontaneous Casting）」16 次。</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2943,7 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Maneuver Mastery</t>
+          <t>Amazing Inspiration</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -2954,7 +2953,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -2964,28 +2963,28 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>驚人靈感
+奇妙靈感</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>戰技熟稔×2
-戰技精通</t>
+          <t>奇妙靈感</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>奇妙靈感×2</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>奇妙靈感</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「奇妙靈感（Amazing Inspiration）」2 次。</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2994,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Unarmed Strike</t>
+          <t>True Inspiration</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -3005,7 +3004,7 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -3015,29 +3014,28 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>真實靈感
+靈感滿溢</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>徒手擊打
-徒手打擊</t>
+          <t>靈感滿溢</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>徒手打擊×22
-徒手擊打×2</t>
+          <t>沒有附英文的定名</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>徒手打擊</t>
+          <t>靈感滿溢</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
+          <t>2 個倉庫都用「靈感滿溢」，只有 mods 另有寫法。</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3045,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Increased Damage Reduction</t>
+          <t>Tenacious Inspiration</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -3057,7 +3055,7 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉＋倉內不一致</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -3067,28 +3065,28 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>頑強靈感
+執著靈感</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>傷害減免
-增強傷害減免</t>
+          <t>執著靈感</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>增強傷害減免×20</t>
+          <t>執著靈感×2</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>增強傷害減免</t>
+          <t>執著靈感</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「增強傷害減免（Increased Damage Reduction）」20 次。</t>
+          <t>CHM v2.33.0 寫「執著靈感（Tenacious Inspiration）」2 次。</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3096,7 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Maneuver Mastery</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
@@ -3123,23 +3121,23 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>引導能量
-能量引導</t>
+          <t>戰技熟稔×2
+戰技精通</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>能量引導×2</t>
-        </is>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>引導能量</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>CHM 內文寫「引導能量」759 次、「能量引導」40 次。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3147,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Spirit</t>
+          <t>Unarmed Strike</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -3159,7 +3157,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>跨倉不一致</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -3169,28 +3167,29 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>精魂</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>魂域</t>
+          <t>徒手擊打
+徒手打擊</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>魂域×4
-英靈×24（倉庫沒用）</t>
+          <t>徒手打擊×22
+徒手擊打×2</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>魂域</t>
+          <t>徒手打擊</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>查過 CHM：薩滿的 Spirit 寫「魂域」，通靈者的 Spirit 寫「英靈」，巫婆庇護主的 Spirits 寫「精魂」，是三個不同東西。這裡兩處（SBC 的施法特性、合集包的職業能力）都是薩滿的，所以建議「魂域」。</t>
+          <t>CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3199,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Low-Light Vision</t>
+          <t>Increased Damage Reduction</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -3225,23 +3224,23 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>低光視力
-昏暗視覺</t>
+          <t>傷害減免
+增強傷害減免</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>昏暗視覺×102</t>
+          <t>增強傷害減免×20</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>昏暗視覺</t>
+          <t>增強傷害減免</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「昏暗視覺（Low-Light Vision）」102 次。</t>
+          <t>CHM v2.33.0 寫「增強傷害減免（Increased Damage Reduction）」20 次。</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3250,7 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Breath Weapon</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -3276,24 +3275,23 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>噴吐武器
-噴吐龍息</t>
+          <t>引導能量
+能量引導</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>噴吐武器×6
-吐息武器×4（倉庫沒用）</t>
+          <t>能量引導×2</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>噴吐武器</t>
+          <t>引導能量</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「噴吐武器（Breath Weapon）」6 次。</t>
+          <t>CHM 內文寫「引導能量」759 次、「能量引導」40 次。</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3301,7 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Wings</t>
+          <t>Spirit</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -3313,7 +3311,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
@@ -3323,28 +3321,28 @@
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>精魂</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>翅膀
-龍翼</t>
+          <t>魂域</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>翅膀×2</t>
-        </is>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>魂域×4
+英靈×24（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>魂域</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
+          <t>已裁定。查過 CHM：薩滿的 Spirit 寫「魂域」，通靈者的 Spirit 寫「英靈」，巫婆庇護主的 Spirits 寫「精魂」，是三個不同東西。這裡兩處（SBC 的施法特性、合集包的職業能力）都是薩滿的，所以建議「魂域」。</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3352,7 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Low-Light Vision</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -3379,23 +3377,23 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>忍法·無常步
-反射閃避</t>
+          <t>低光視力
+昏暗視覺</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>反射閃避×20</t>
+          <t>昏暗視覺×102</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>反射閃避</t>
+          <t>昏暗視覺</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「反射閃避（Evasion）」20 次；CHM 裡找不到「忍法·」這種寫法。</t>
+          <t>CHM v2.33.0 寫「昏暗視覺（Low-Light Vision）」102 次。</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3403,7 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>Breath Weapon</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
@@ -3415,7 +3413,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>跨倉不一致</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -3425,27 +3423,29 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>秘示</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>秘示域</t>
+          <t>噴吐武器
+噴吐龍息</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>秘示域×12</t>
+          <t>噴吐武器×6
+吐息武器×4（倉庫沒用）</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>秘示域</t>
+          <t>噴吐武器</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「秘示域（Mystery）」12 次。</t>
+          <t>CHM v2.33.0 寫「噴吐武器（Breath Weapon）」6 次。</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Knockback</t>
+          <t>Wings</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -3480,23 +3480,23 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>一擊即飛
-擊飛</t>
+          <t>翅膀
+龍翼</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>擊飛×8</t>
-        </is>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>擊飛</t>
+          <t>翅膀×2</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「擊飛（Knockback）」8 次。</t>
+          <t>「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Elemental Body</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
@@ -3531,23 +3531,23 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>元素之軀
-元素身軀</t>
+          <t>忍法·無常步
+反射閃避</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>元素形態×2（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>元素形態</t>
+          <t>反射閃避×20</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>反射閃避</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>已裁定。回覆寫的是「元素型態」，但 CHM 寫「元素形態」99 次、「元素型態」0 次，先照 CHM 記「形態」，要用「型態」請再說。</t>
+          <t>CHM v2.33.0 寫「反射閃避（Evasion）」20 次；CHM 裡找不到「忍法·」這種寫法。</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Superstition</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>倉內不一致</t>
+          <t>跨倉不一致</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -3577,28 +3577,27 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>秘示</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>神秘迷信
-迷信</t>
+          <t>秘示域</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>迷信×14</t>
+          <t>秘示域×12</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>迷信</t>
+          <t>秘示域</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「迷信（Superstition）」14 次。</t>
+          <t>CHM v2.33.0 寫「秘示域（Mystery）」12 次。</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3607,7 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Abundant Step</t>
+          <t>Knockback</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
@@ -3633,23 +3632,23 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>天遁術
-遁術</t>
+          <t>一擊即飛
+擊飛</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>遁術×4</t>
+          <t>擊飛×8</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>遁術</t>
+          <t>擊飛</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「遁術（Abundant Step）」4 次。</t>
+          <t>CHM v2.33.0 寫「擊飛（Knockback）」8 次。</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3658,7 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Major Magic</t>
+          <t>Elemental Body</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -3684,23 +3683,23 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>高等魔法
-高級魔法</t>
+          <t>元素之軀
+元素身軀</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>高級魔法×22</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>高級魔法</t>
+          <t>元素形態×2（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>元素形態</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「高級魔法（Major Magic）」22 次。</t>
+          <t>已裁定，跟 CHM 一致（CHM 寫「元素形態」99 次）。</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3709,7 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Minor Magic</t>
+          <t>Superstition</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
@@ -3735,23 +3734,23 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>次等魔法
-次級魔法</t>
+          <t>神秘迷信
+迷信</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>次級魔法×40</t>
+          <t>迷信×14</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>次級魔法</t>
+          <t>迷信</t>
         </is>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「次級魔法（Minor Magic）」40 次。</t>
+          <t>CHM v2.33.0 寫「迷信（Superstition）」14 次。</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3760,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Order of the Beast</t>
+          <t>Abundant Step</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -3786,24 +3785,23 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>獸之騎士團
-狂獸騎士團</t>
+          <t>天遁術
+遁術</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>狂獸騎士團×6
-獸之騎士團×3</t>
+          <t>遁術×4</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>狂獸騎士團</t>
+          <t>遁術</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「狂獸騎士團（Order of the Beast）」6 次。</t>
+          <t>CHM v2.33.0 寫「遁術（Abundant Step）」4 次。</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3811,7 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Resiliency</t>
+          <t>Major Magic</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
@@ -3838,24 +3836,23 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>堅韌身軀
-韌性</t>
+          <t>高等魔法
+高級魔法</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>韌性×6
-堅韌身軀×2</t>
+          <t>高級魔法×22</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>韌性</t>
+          <t>高級魔法</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「韌性（Resiliency）」6 次。</t>
+          <t>CHM v2.33.0 寫「高級魔法（Major Magic）」22 次。</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3862,7 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Acid Dart</t>
+          <t>Minor Magic</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -3890,23 +3887,23 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>強酸鏢
-酸鏢</t>
+          <t>次等魔法
+次級魔法</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>次級魔法×40</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>次級魔法</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「次級魔法（Minor Magic）」40 次。</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3913,7 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Intimidating Glare</t>
+          <t>Order of the Beast</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
@@ -3941,23 +3938,24 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>威嚇凝視
-威嚇怒視</t>
+          <t>獸之騎士團
+狂獸騎士團</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>威嚇凝視×18</t>
+          <t>狂獸騎士團×6
+獸之騎士團×3</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>威嚇凝視</t>
+          <t>狂獸騎士團</t>
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「威嚇凝視（Intimidating Glare）」18 次。</t>
+          <t>CHM v2.33.0 寫「狂獸騎士團（Order of the Beast）」6 次。</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3965,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Smoke Bomb</t>
+          <t>Resiliency</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -3992,23 +3990,24 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>忍法·迷蹤
-煙霧炸彈</t>
+          <t>堅韌身軀
+韌性</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>煙霧彈×3（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>煙霧彈</t>
+          <t>韌性×6
+堅韌身軀×2</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>韌性</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>已裁定，跟 CHM 一致。</t>
+          <t>CHM v2.33.0 寫「韌性（Resiliency）」6 次。</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4017,7 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Guarded Stance</t>
+          <t>Acid Dart</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
@@ -4043,23 +4042,23 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>守衛姿態
-防衛戰姿</t>
+          <t>強酸鏢
+酸鏢</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>守衛姿態×10</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>守衛姿態</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「守衛姿態（Guarded Stance）」10 次。</t>
+          <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4068,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Terrifying Howl</t>
+          <t>Intimidating Glare</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -4094,23 +4093,23 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>可怖狂嚎
-怖懼狂嚎</t>
+          <t>威嚇凝視
+威嚇怒視</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>怖懼狂嚎×10</t>
+          <t>威嚇凝視×18</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>怖懼狂嚎</t>
+          <t>威嚇凝視</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
+          <t>CHM v2.33.0 寫「威嚇凝視（Intimidating Glare）」18 次。</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4119,7 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Animal Fury</t>
+          <t>Smoke Bomb</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
@@ -4145,23 +4144,23 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>獸性之怒
-野性之怒</t>
+          <t>忍法·迷蹤
+煙霧炸彈</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>野性之怒×28</t>
-        </is>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>野性之怒</t>
+          <t>煙霧彈×3（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>煙霧彈</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「野性之怒（Animal Fury）」28 次。</t>
+          <t>已裁定，跟 CHM 一致。</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4170,7 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Aura of Despair</t>
+          <t>Guarded Stance</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -4196,23 +4195,23 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>絕望光環
-絕望靈光</t>
+          <t>守衛姿態
+防衛戰姿</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>絕望靈氳（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I69" s="14" t="inlineStr">
-        <is>
-          <t>絕望靈氳</t>
+          <t>守衛姿態×10</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>守衛姿態</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>已裁定，跟 CHM 及系統介面的「靈氳」一致。</t>
+          <t>CHM v2.33.0 寫「守衛姿態（Guarded Stance）」10 次。</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4221,7 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>Auspicious Mark</t>
+          <t>Terrifying Howl</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -4247,23 +4246,23 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>吉祥印記
-吉祥烙記</t>
+          <t>可怖狂嚎
+怖懼狂嚎</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>吉祥烙記×2</t>
+          <t>怖懼狂嚎×10</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>吉祥烙記</t>
+          <t>怖懼狂嚎</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「吉祥烙記（Auspicious Mark）」2 次。</t>
+          <t>CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4272,7 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Deadly Accuracy</t>
+          <t>Animal Fury</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -4298,23 +4297,23 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>死亡精準
-致命精確</t>
+          <t>獸性之怒
+野性之怒</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>致命精確×4</t>
+          <t>野性之怒×28</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>致命精確</t>
+          <t>野性之怒</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「致命精確（Deadly Accuracy）」4 次。</t>
+          <t>CHM v2.33.0 寫「野性之怒（Animal Fury）」28 次。</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4323,7 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>High Jump</t>
+          <t>Aura of Despair</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -4349,23 +4348,23 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>輕功
-輕身縱</t>
+          <t>絕望光環
+絕望靈光</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>輕功×2</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>輕功</t>
+          <t>絕望靈氳（倉庫沒用）</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>絕望靈氳</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「輕功（High Jump）」2 次。</t>
+          <t>已裁定，跟 CHM 及系統介面的「靈氳」一致。</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4374,7 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Poison Resistance</t>
+          <t>Auspicious Mark</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -4400,24 +4399,23 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>毒素抗力
-毒性抗力</t>
+          <t>吉祥印記
+吉祥烙記</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>毒性抗力×6
-毒素抗力×4</t>
-        </is>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>吉祥烙記×2</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>吉祥烙記</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「吉祥烙記（Auspicious Mark）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4425,7 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>Dazing Touch</t>
+          <t>Deadly Accuracy</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -4452,23 +4450,23 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>恍惚接觸
-眩目之觸</t>
+          <t>死亡精準
+致命精確</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>致命精確×4</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>致命精確</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「致命精確（Deadly Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4476,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Ground Breaker</t>
+          <t>High Jump</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -4503,23 +4501,23 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>大地之擊
-撼地一擊</t>
+          <t>輕功
+輕身縱</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>大地之擊×2</t>
+          <t>輕功×2</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>大地之擊</t>
+          <t>輕功</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「大地之擊（Ground Breaker）」2 次。</t>
+          <t>CHM v2.33.0 寫「輕功（High Jump）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4527,7 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Skill Mastery</t>
+          <t>Poison Resistance</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -4554,24 +4552,24 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>技能專精
-技藝精湛</t>
+          <t>毒素抗力
+毒性抗力</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>技能專精×40
-技藝精湛×4</t>
-        </is>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>技能專精</t>
+          <t>毒性抗力×6
+毒素抗力×4</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「技能專精（Skill Mastery）」40 次。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4579,7 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Swift Foot</t>
+          <t>Dazing Touch</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -4606,24 +4604,23 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>迅捷腳步
-迅足</t>
+          <t>恍惚接觸
+眩目之觸</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>迅足×8
-快步×4（倉庫沒用）</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>迅足</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「迅足（Swift Foot）」8 次。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4630,7 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Bardic Knowledge</t>
+          <t>Ground Breaker</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
@@ -4658,23 +4655,23 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>軼聞知識
-逸聞知識</t>
+          <t>大地之擊
+撼地一擊</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>逸聞知識×4</t>
+          <t>大地之擊×2</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>逸聞知識</t>
+          <t>大地之擊</t>
         </is>
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「逸聞知識（Bardic Knowledge）」4 次。</t>
+          <t>CHM v2.33.0 寫「大地之擊（Ground Breaker）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4681,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Bleeding Blow</t>
+          <t>Skill Mastery</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -4709,23 +4706,24 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>出血打擊
-流血猛擊</t>
+          <t>技能專精
+技藝精湛</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>流血猛擊×4</t>
+          <t>技能專精×40
+技藝精湛×4</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
-          <t>流血猛擊</t>
+          <t>技能專精</t>
         </is>
       </c>
       <c r="J79" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「流血猛擊（Bleeding Blow）」4 次。</t>
+          <t>CHM v2.33.0 寫「技能專精（Skill Mastery）」40 次。</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4733,7 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>Crippling Blow</t>
+          <t>Swift Foot</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -4760,23 +4758,24 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>致殘打擊
-致殘猛擊</t>
+          <t>迅捷腳步
+迅足</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>致殘猛擊×2</t>
+          <t>迅足×8
+快步×4（倉庫沒用）</t>
         </is>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
-          <t>致殘猛擊</t>
+          <t>迅足</t>
         </is>
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「致殘猛擊（Crippling Blow）」2 次。</t>
+          <t>CHM v2.33.0 寫「迅足（Swift Foot）」8 次。</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4785,7 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Eater of Magic</t>
+          <t>Bardic Knowledge</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -4811,23 +4810,23 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>享用魔力
-吞噬魔法</t>
+          <t>軼聞知識
+逸聞知識</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>吞噬魔法×6</t>
+          <t>逸聞知識×4</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>吞噬魔法</t>
+          <t>逸聞知識</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「吞噬魔法（Eater of Magic）」6 次。</t>
+          <t>CHM v2.33.0 寫「逸聞知識（Bardic Knowledge）」4 次。</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4836,7 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>Lasting Poison</t>
+          <t>Bleeding Blow</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -4862,23 +4861,23 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>持久毒藥
-毒性持續</t>
+          <t>出血打擊
+流血猛擊</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>毒性持續×2</t>
+          <t>流血猛擊×4</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
-          <t>毒性持續</t>
+          <t>流血猛擊</t>
         </is>
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「毒性持續（Lasting Poison）」2 次。</t>
+          <t>CHM v2.33.0 寫「流血猛擊（Bleeding Blow）」4 次。</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4887,7 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Nimble Climber</t>
+          <t>Crippling Blow</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -4913,24 +4912,23 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>機敏攀巖者
-飛簷走壁</t>
+          <t>致殘打擊
+致殘猛擊</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>飛簷走壁×2
-和靈動攀爬×2（倉庫沒用）</t>
+          <t>致殘猛擊×2</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
-          <t>飛簷走壁</t>
+          <t>致殘猛擊</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「飛簷走壁（Nimble Climber）」2 次。</t>
+          <t>CHM v2.33.0 寫「致殘猛擊（Crippling Blow）」2 次。</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4938,7 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Raging Leaper</t>
+          <t>Eater of Magic</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -4965,23 +4963,23 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>狂暴躍者
-狂暴跳躍</t>
+          <t>享用魔力
+吞噬魔法</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>狂暴跳躍×14</t>
+          <t>吞噬魔法×6</t>
         </is>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
-          <t>狂暴跳躍</t>
+          <t>吞噬魔法</t>
         </is>
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「狂暴跳躍（Raging Leaper）」14 次。</t>
+          <t>CHM v2.33.0 寫「吞噬魔法（Eater of Magic）」6 次。</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4989,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Raging Swimmer</t>
+          <t>Lasting Poison</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -5016,23 +5014,23 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>狂暴泳者
-狂暴遊者</t>
+          <t>持久毒藥
+毒性持續</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>狂暴遊者×10</t>
+          <t>毒性持續×2</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>狂暴遊者</t>
+          <t>毒性持續</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「狂暴遊者（Raging Swimmer）」10 次。</t>
+          <t>CHM v2.33.0 寫「毒性持續（Lasting Poison）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5040,7 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>Sharpened Accuracy</t>
+          <t>Nimble Climber</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -5067,23 +5065,24 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>敏銳精準
-敏銳精確</t>
+          <t>機敏攀巖者
+飛簷走壁</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>敏銳精確×2</t>
+          <t>飛簷走壁×2
+和靈動攀爬×2（倉庫沒用）</t>
         </is>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>敏銳精確</t>
+          <t>飛簷走壁</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「敏銳精確（Sharpened Accuracy）」2 次。</t>
+          <t>CHM v2.33.0 寫「飛簷走壁（Nimble Climber）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5092,7 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Sprint</t>
+          <t>Raging Leaper</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -5118,23 +5117,23 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>奮力衝刺
-奮勇衝刺</t>
+          <t>狂暴躍者
+狂暴跳躍</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>奮力衝刺×6</t>
+          <t>狂暴跳躍×14</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>奮力衝刺</t>
+          <t>狂暴跳躍</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「奮力衝刺（Sprint）」6 次。</t>
+          <t>CHM v2.33.0 寫「狂暴跳躍（Raging Leaper）」14 次。</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5143,7 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>Sudden Speed</t>
+          <t>Raging Swimmer</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -5169,23 +5168,23 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>瞬時加速
-電瞬步</t>
+          <t>狂暴泳者
+狂暴遊者</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>狂暴遊者×10</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>狂暴遊者</t>
         </is>
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「狂暴遊者（Raging Swimmer）」10 次。</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5194,7 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Unexpected Strike</t>
+          <t>Sharpened Accuracy</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -5220,23 +5219,23 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>意外之擊
-詭擊</t>
+          <t>敏銳精準
+敏銳精確</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>詭擊×6</t>
+          <t>敏銳精確×2</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>詭擊</t>
+          <t>敏銳精確</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「詭擊（Unexpected Strike）」6 次。</t>
+          <t>CHM v2.33.0 寫「敏銳精確（Sharpened Accuracy）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5245,7 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Witch Hunter</t>
+          <t>Sprint</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
@@ -5271,23 +5270,23 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>女巫獵人
-獵巫人</t>
+          <t>奮力衝刺
+奮勇衝刺</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>獵巫人×8</t>
+          <t>奮力衝刺×6</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>獵巫人</t>
+          <t>奮力衝刺</t>
         </is>
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「獵巫人（Witch Hunter）」8 次。</t>
+          <t>CHM v2.33.0 寫「奮力衝刺（Sprint）」6 次。</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5296,7 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Aberrant Form</t>
+          <t>Sudden Speed</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -5322,8 +5321,8 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>化身異怪
-異怪形態</t>
+          <t>瞬時加速
+電瞬步</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -5348,7 +5347,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Brain Drain</t>
+          <t>Unexpected Strike</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
@@ -5373,23 +5372,23 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>意識鑽刺
-意識鑽探</t>
+          <t>意外之擊
+詭擊</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>意識鑽刺×2</t>
+          <t>詭擊×6</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>意識鑽刺</t>
+          <t>詭擊</t>
         </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「意識鑽刺（Brain Drain）」2 次。</t>
+          <t>CHM v2.33.0 寫「詭擊（Unexpected Strike）」6 次。</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5398,7 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Clear Mind</t>
+          <t>Witch Hunter</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -5424,23 +5423,23 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>心如堅鋼
-心若明鏡</t>
+          <t>女巫獵人
+獵巫人</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>心如堅鋼×10</t>
+          <t>獵巫人×8</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>心如堅鋼</t>
+          <t>獵巫人</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「心如堅鋼（Clear Mind）」10 次。</t>
+          <t>CHM v2.33.0 寫「獵巫人（Witch Hunter）」8 次。</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5449,7 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Fearless Rage</t>
+          <t>Aberrant Form</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
@@ -5475,23 +5474,23 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>無懼狂暴
-無畏狂暴</t>
+          <t>化身異怪
+異怪形態</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>無懼狂暴×6</t>
-        </is>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>無懼狂暴</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「無懼狂暴（Fearless Rage）」6 次。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5500,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Flesh Wound</t>
+          <t>Brain Drain</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -5526,23 +5525,23 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>不屈武勇
-皮外小傷</t>
+          <t>意識鑽刺
+意識鑽探</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>不屈武勇×4</t>
+          <t>意識鑽刺×2</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
-          <t>不屈武勇</t>
+          <t>意識鑽刺</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「不屈武勇（Flesh Wound）」4 次。</t>
+          <t>CHM v2.33.0 寫「意識鑽刺（Brain Drain）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5551,7 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Improved Quarry</t>
+          <t>Clear Mind</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -5577,23 +5576,23 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>精通狩獵目標
-高等狩獵目標</t>
+          <t>心如堅鋼
+心若明鏡</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>高等狩獵目標×4</t>
+          <t>心如堅鋼×10</t>
         </is>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
-          <t>高等狩獵目標</t>
+          <t>心如堅鋼</t>
         </is>
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
+          <t>CHM v2.33.0 寫「心如堅鋼（Clear Mind）」10 次。</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5602,7 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Inspire Ferocity</t>
+          <t>Fearless Rage</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -5628,23 +5627,23 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>狂怒之示
-狂怒激發</t>
+          <t>無懼狂暴
+無畏狂暴</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>狂怒激發×2</t>
+          <t>無懼狂暴×6</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>狂怒激發</t>
+          <t>無懼狂暴</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
+          <t>CHM v2.33.0 寫「無懼狂暴（Fearless Rage）」6 次。</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5653,7 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Lethal Accuracy</t>
+          <t>Flesh Wound</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -5679,23 +5678,23 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>致命精準
-致死精確</t>
+          <t>不屈武勇
+皮外小傷</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>致死精確×4</t>
+          <t>不屈武勇×4</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
-          <t>致死精確</t>
+          <t>不屈武勇</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「致死精確（Lethal Accuracy）」4 次。</t>
+          <t>CHM v2.33.0 寫「不屈武勇（Flesh Wound）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5704,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Life Sight</t>
+          <t>Improved Quarry</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -5730,23 +5729,23 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>感知生命
-生命視野</t>
+          <t>精通狩獵目標
+高等狩獵目標</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>高等狩獵目標×4</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>高等狩獵目標</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5755,7 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Light Steps</t>
+          <t>Inspire Ferocity</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
@@ -5781,23 +5780,23 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>凌波步
-輕身步</t>
+          <t>狂怒之示
+狂怒激發</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>沒有附英文的定名</t>
-        </is>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+          <t>狂怒激發×2</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>狂怒激發</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5806,7 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Quick Reflexes</t>
+          <t>Lethal Accuracy</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -5832,23 +5831,23 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>快速反射
-超速反射</t>
+          <t>致命精準
+致死精確</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>超速反射×8</t>
+          <t>致死精確×4</t>
         </is>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
-          <t>超速反射</t>
+          <t>致死精確</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「超速反射（Quick Reflexes）」8 次。</t>
+          <t>CHM v2.33.0 寫「致死精確（Lethal Accuracy）」4 次。</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5857,7 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Roused Anger</t>
+          <t>Life Sight</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
@@ -5883,23 +5882,23 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>無邊怒火
-激發怒意</t>
+          <t>感知生命
+生命視野</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>無邊怒火×10</t>
-        </is>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>無邊怒火</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「無邊怒火（Roused Anger）」10 次。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5908,7 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Slowing Strike</t>
+          <t>Light Steps</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -5934,8 +5933,8 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>延緩打擊
-遲緩一擊</t>
+          <t>凌波步
+輕身步</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -5960,7 +5959,7 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>Smasher</t>
+          <t>Quick Reflexes</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
@@ -5985,24 +5984,23 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>破壞者
-野蠻破壞</t>
+          <t>快速反射
+超速反射</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>破壞者×4
-粉碎者×2（倉庫沒用）</t>
+          <t>超速反射×8</t>
         </is>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
-          <t>破壞者</t>
+          <t>超速反射</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「破壞者（Smasher）」4 次。</t>
+          <t>CHM v2.33.0 寫「超速反射（Quick Reflexes）」8 次。</t>
         </is>
       </c>
     </row>
@@ -6012,47 +6010,48 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>（文本）</t>
+          <t>Roused Anger</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>文本×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>文本×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>文本×384</t>
+          <t>無邊怒火
+激發怒意</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>內文</t>
+          <t>無邊怒火×10</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>無邊怒火</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。法術欄位的「見文本」改成「見內文」，介面的「文本頁」改成「內文頁」。</t>
+          <t>CHM v2.33.0 寫「無邊怒火（Roused Anger）」10 次。</t>
         </is>
       </c>
     </row>
@@ -6062,17 +6061,17 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>（信息）</t>
+          <t>Slowing Strike</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -6087,22 +6086,23 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>信息×211</t>
+          <t>延緩打擊
+遲緩一擊</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>訊息</t>
+          <t>沒有附英文的定名</t>
+        </is>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>待裁定</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「訊息」，mods、compendium 已經這樣用。</t>
+          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -6112,17 +6112,17 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>（激活）</t>
+          <t>Smasher</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>職業能力名</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>倉內不一致</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -6137,22 +6137,24 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>激活×59</t>
+          <t>破壞者
+野蠻破壞</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>破壞者×4
+粉碎者×2（倉庫沒用）</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
-          <t>啟動</t>
+          <t>破壞者</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t>全是合集包內文的「激活某能力」；合集包已有 197 處寫「啟動」。</t>
+          <t>CHM v2.33.0 寫「破壞者（Smasher）」4 次。</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6164,7 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>（圖標）</t>
+          <t>（文本）</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
@@ -6177,17 +6179,17 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>圖標×12</t>
+          <t>文本×8</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>圖標×25</t>
+          <t>文本×8</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>圖標×3</t>
+          <t>文本×384</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -6195,14 +6197,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>圖示</t>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>內文</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「圖示」，mods 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。法術欄位的「見文本」改成「見內文」，介面的「文本頁」改成「內文頁」。</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6214,7 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>（設置）</t>
+          <t>（信息）</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -6227,7 +6229,7 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>設置×33</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -6237,7 +6239,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>信息×211</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -6247,12 +6249,12 @@
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>訊息</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「設定」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「訊息」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6264,7 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>（添加）</t>
+          <t>（激活）</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
@@ -6287,7 +6289,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>添加×29</t>
+          <t>激活×59</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -6295,14 +6297,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>加到</t>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>啟動</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。依句子改成「加到」或「加上」，例如「添加到豁免加值上」→「加到豁免加值上」。</t>
+          <t>全是合集包內文的「激活某能力」；合集包已有 197 處寫「啟動」。</t>
         </is>
       </c>
     </row>
@@ -6312,32 +6314,32 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>（复）</t>
+          <t>（圖標）</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>圖標×12</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>圖標×25</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>复×27</t>
+          <t>圖標×3</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -6347,12 +6349,12 @@
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>復</t>
+          <t>圖示</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>「复」是簡體字，同一個詞在倉庫其他地方已經寫成「復」。</t>
+          <t>對岸用語；台灣寫「圖示」，mods 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6364,7 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>（數據）</t>
+          <t>（設置）</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -6377,17 +6379,17 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>設置×33</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>數據×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>數據×23</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -6397,12 +6399,12 @@
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
-          <t>資料</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「資料」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「設定」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6414,7 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>（鏈接）</t>
+          <t>（添加）</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -6437,7 +6439,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>鏈接×25</t>
+          <t>添加×29</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -6445,14 +6447,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>連結</t>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>加到</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「連結」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。依句子改成「加到」或「加上」，例如「添加到豁免加值上」→「加到豁免加值上」。</t>
         </is>
       </c>
     </row>
@@ -6462,17 +6464,17 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>（質量）</t>
+          <t>（复）</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -6487,7 +6489,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>質量×24</t>
+          <t>复×27</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -6497,12 +6499,12 @@
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
-          <t>品質</t>
+          <t>復</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「品質」，compendium 已經這樣用。</t>
+          <t>「复」是簡體字，同一個詞在倉庫其他地方已經寫成「復」。</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6514,7 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>（界面）</t>
+          <t>（數據）</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -6532,12 +6534,12 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>界面×21</t>
+          <t>數據×2</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>界面×2</t>
+          <t>數據×23</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -6545,14 +6547,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I115" s="14" t="inlineStr">
-        <is>
-          <t>介面</t>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>資料</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「介面」。</t>
+          <t>對岸用語；台灣寫「資料」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6564,7 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>（拖拽）</t>
+          <t>（鏈接）</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
@@ -6582,12 +6584,12 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>拖拽×22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>鏈接×25</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -6597,12 +6599,12 @@
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
-          <t>拖曳</t>
+          <t>連結</t>
         </is>
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「拖曳」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「連結」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6614,7 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>（變量）</t>
+          <t>（質量）</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -6627,17 +6629,17 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>變量×10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>變量×4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>變量×7</t>
+          <t>質量×24</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -6647,12 +6649,12 @@
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>變數</t>
+          <t>品質</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「變數」，compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「品質」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6664,7 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>（窗口）</t>
+          <t>（界面）</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
@@ -6682,12 +6684,12 @@
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>窗口×10</t>
+          <t>界面×21</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>窗口×8</t>
+          <t>界面×2</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -6697,12 +6699,12 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>視窗</t>
+          <t>介面</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「視窗」。</t>
+          <t>已裁定（只改繁體版）。台灣寫「介面」。</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6714,7 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>（自定義）</t>
+          <t>（拖拽）</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -6727,17 +6729,17 @@
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>自定義×16</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>拖拽×22</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>自定義×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -6747,12 +6749,12 @@
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
-          <t>自訂</t>
+          <t>拖曳</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「自訂」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「拖曳」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6764,7 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>（全局）</t>
+          <t>（變量）</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
@@ -6777,17 +6779,17 @@
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>全局×1</t>
+          <t>變量×10</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>全局×14</t>
+          <t>變量×4</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>變量×7</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -6797,12 +6799,12 @@
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
-          <t>全域</t>
+          <t>變數</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「全域」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「變數」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6814,7 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>（創建）</t>
+          <t>（窗口）</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -6832,12 +6834,12 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>窗口×10</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>創建×14</t>
+          <t>窗口×8</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -6845,14 +6847,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>建立</t>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>視窗</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「建立」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。台灣寫「視窗」。</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6864,7 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>（用戶）</t>
+          <t>（自定義）</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
@@ -6877,17 +6879,17 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>用戶×1</t>
+          <t>自定義×16</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>用戶×8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>自定義×1</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -6897,12 +6899,12 @@
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
-          <t>使用者</t>
+          <t>自訂</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「使用者」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「自訂」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6914,7 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>（調試）</t>
+          <t>（全局）</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -6927,12 +6929,12 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>全局×1</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>調試×8</t>
+          <t>全局×14</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -6945,14 +6947,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I123" s="14" t="inlineStr">
-        <is>
-          <t>偵錯</t>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>全域</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「偵錯」。</t>
+          <t>對岸用語；台灣寫「全域」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6964,7 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>（控件）</t>
+          <t>（創建）</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
@@ -6982,12 +6984,12 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>控件×6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>創建×14</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -6995,14 +6997,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I124" s="14" t="inlineStr">
-        <is>
-          <t>控制項</t>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>建立</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「控制項」。</t>
+          <t>對岸用語；台灣寫「建立」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7014,7 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>（運行）</t>
+          <t>（用戶）</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -7027,12 +7029,12 @@
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>運行×3</t>
+          <t>用戶×1</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>運行×1</t>
+          <t>用戶×8</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -7047,12 +7049,12 @@
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
-          <t>執行</t>
+          <t>使用者</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「執行」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「使用者」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7064,7 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>（令牌）</t>
+          <t>（調試）</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
@@ -7082,7 +7084,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>令牌×4</t>
+          <t>調試×8</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -7095,14 +7097,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>指示物</t>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>偵錯</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「指示物」，pf1-zhtw、mods 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。台灣寫「偵錯」。</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7114,7 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>（字段）</t>
+          <t>（控件）</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -7132,7 +7134,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>字段×4</t>
+          <t>控件×6</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -7145,14 +7147,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>欄位</t>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>控制項</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「欄位」，pf1-zhtw、compendium 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。台灣寫「控制項」。</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7164,7 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>（默認）</t>
+          <t>（運行）</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
@@ -7177,17 +7179,17 @@
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>運行×3</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>運行×1</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>默認×4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -7197,12 +7199,12 @@
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
-          <t>預設</t>
+          <t>執行</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「預設」，pf1-zhtw、mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「執行」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7214,7 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>（搜索）</t>
+          <t>（令牌）</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -7227,12 +7229,12 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>搜索×3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>令牌×4</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -7247,12 +7249,12 @@
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>搜尋</t>
+          <t>指示物</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「搜尋」，mods、compendium 已經這樣用。</t>
+          <t>對岸用語；台灣寫「指示物」，pf1-zhtw、mods 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7264,7 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>（兼容）</t>
+          <t>（字段）</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
@@ -7277,17 +7279,17 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>兼容×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>字段×4</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>兼容×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -7297,12 +7299,12 @@
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
-          <t>相容</t>
+          <t>欄位</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「相容」，mods 已經這樣用。</t>
+          <t>對岸用語；台灣寫「欄位」，pf1-zhtw、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7314,7 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>（代碼）</t>
+          <t>（默認）</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -7327,7 +7329,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>代碼×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -7337,7 +7339,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>代碼×1</t>
+          <t>默認×4</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -7345,14 +7347,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>程式碼</t>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>預設</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「程式碼」。</t>
+          <t>對岸用語；台灣寫「預設」，pf1-zhtw、mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7364,7 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>（批量）</t>
+          <t>（搜索）</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
@@ -7377,12 +7379,12 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>搜索×3</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>批量×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -7395,14 +7397,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I132" s="14" t="inlineStr">
-        <is>
-          <t>批次</t>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>搜尋</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「批次」。</t>
+          <t>對岸用語；台灣寫「搜尋」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7414,7 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>（攝像機）</t>
+          <t>（兼容）</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -7427,17 +7429,17 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>兼容×2</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>攝像機×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>兼容×1</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -7445,14 +7447,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I133" s="14" t="inlineStr">
-        <is>
-          <t>攝影機</t>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>相容</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「攝影機」。</t>
+          <t>對岸用語；台灣寫「相容」，mods 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7464,7 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>（粘貼）</t>
+          <t>（代碼）</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
@@ -7477,17 +7479,17 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代碼×1</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>粘貼×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代碼×1</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -7495,14 +7497,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>貼上</t>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>程式碼</t>
         </is>
       </c>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「貼上」，mods、compendium 已經這樣用。</t>
+          <t>已裁定（只改繁體版）。台灣寫「程式碼」。</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7514,7 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>（刷新）</t>
+          <t>（批量）</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -7532,12 +7534,12 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>批量×2</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>刷新×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -7545,14 +7547,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>批次</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>這裡是「刷新持續時間」（重新計時），介面用的「重新整理」不適用，需要人看語境。</t>
+          <t>已裁定（只改繁體版）。台灣寫「批次」。</t>
         </is>
       </c>
     </row>
@@ -7562,17 +7564,17 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>（钟）</t>
+          <t>（攝像機）</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>簡體字</t>
+          <t>對岸用語</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
@@ -7582,12 +7584,12 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>攝像機×2</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>钟×2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -7595,14 +7597,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>鐘</t>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>攝影機</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>「钟」是簡體字，同一個詞在倉庫其他地方已經寫成「鐘」。</t>
+          <t>已裁定（只改繁體版）。台灣寫「攝影機」。</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7614,7 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>（導入）</t>
+          <t>（粘貼）</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -7627,12 +7629,12 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>導入×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>粘貼×2</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -7647,12 +7649,12 @@
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
-          <t>匯入</t>
+          <t>貼上</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>對岸用語；台灣寫「匯入」，mods 已經這樣用。</t>
+          <t>對岸用語；台灣寫「貼上」，mods、compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7664,7 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>（服務器）</t>
+          <t>（刷新）</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
@@ -7677,7 +7679,7 @@
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>服務器×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
@@ -7687,7 +7689,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>刷新×2</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -7697,12 +7699,12 @@
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>伺服器</t>
+          <t>重置</t>
         </is>
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「伺服器」。</t>
+          <t>已裁定（只改繁體版）。「刷新持續時間」→「重置持續時間」、「刷新時效」→「重置時效」。</t>
         </is>
       </c>
     </row>
@@ -7712,17 +7714,17 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>（光標）</t>
+          <t>（钟）</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>對岸用語</t>
+          <t>簡體字</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -7732,12 +7734,12 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>光標×1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>钟×2</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -7745,14 +7747,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>游標</t>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>鐘</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>已裁定（只改繁體版）。台灣寫「游標」。</t>
+          <t>「钟」是簡體字，同一個詞在倉庫其他地方已經寫成「鐘」。</t>
         </is>
       </c>
     </row>
@@ -7762,52 +7764,202 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
+          <t>（導入）</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>導入×1</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>匯入</t>
+        </is>
+      </c>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語；台灣寫「匯入」，mods 已經這樣用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>（服務器）</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>服務器×1</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>伺服器</t>
+        </is>
+      </c>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>已裁定（只改繁體版）。台灣寫「伺服器」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>（光標）</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>對岸用語</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>光標×1</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>游標</t>
+        </is>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>已裁定（只改繁體版）。台灣寫「游標」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
           <t>（音頻）</t>
         </is>
       </c>
-      <c r="C140" s="12" t="inlineStr">
+      <c r="C143" s="12" t="inlineStr">
         <is>
           <t>對岸用語</t>
         </is>
       </c>
-      <c r="D140" s="12" t="inlineStr">
+      <c r="D143" s="12" t="inlineStr">
         <is>
           <t>對岸用語</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F140" s="12" t="inlineStr">
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
         <is>
           <t>音頻×1</t>
         </is>
       </c>
-      <c r="G140" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
         <is>
           <t>音訊</t>
         </is>
       </c>
-      <c r="J140" s="12" t="inlineStr">
+      <c r="J143" s="12" t="inlineStr">
         <is>
           <t>對岸用語；台灣寫「音訊」，compendium 已經這樣用。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J140"/>
+  <autoFilter ref="A1:J143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8543,7 +8695,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定。回覆寫的是「元素型態」，但 CHM 寫「元素形態」99 次、「元素型態」0 次，先照 CHM 記「形態」，要用「型態」請再說。</t>
+          <t>跟繁體版同一條，繁體版已裁定，跟 CHM 一致（CHM 寫「元素形態」99 次）。</t>
         </is>
       </c>
     </row>

--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -138,9 +138,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +585,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>已裁定（32 條）。維護者 2026-10-17 回覆決定的譯名。</t>
+          <t>已裁定（42 條）。維護者 2026-10-17 回覆決定的譯名。</t>
         </is>
       </c>
     </row>
@@ -612,7 +609,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>待裁定（10 條）。拿不準，需要人來決定。</t>
+          <t>待裁定（0 條）。拿不準，需要人來決定。</t>
         </is>
       </c>
     </row>
@@ -3130,14 +3127,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>維持：先知「戰技熟稔」／魔戰士「戰技精通」</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -3489,14 +3486,14 @@
           <t>翅膀×2</t>
         </is>
       </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>維持：鍊金術師「翅膀」／術士「龍翼」</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -4051,14 +4048,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>牧師「酸鏢」維持；法師改「酸蝕鏢」</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>已裁定，照 CHM：不同職業的同名能力。CHM 牧師領域寫「酸鏢」，法師學派寫「酸蝕鏢」；合集包法師版寫「強酸鏢」，要改成「酸蝕鏢」（也跟 Acid→酸蝕 的決定一致）。</t>
         </is>
       </c>
     </row>
@@ -4562,14 +4559,14 @@
 毒素抗力×4</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>維持：鍊金術師「毒性抗力」／調查員「毒素抗力」</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -4613,14 +4610,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>維持：牧師「恍惚接觸」／法師「眩目之觸」</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -5330,14 +5327,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>維持：秘學士「瞬時加速」／武僧（Unchained）「電瞬步」</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -5483,14 +5480,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>維持：術士「異怪形態」／血脈狂怒者「化身異怪」</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -5891,14 +5888,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>維持：法師「生命視野」／薩滿「感知生命」</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -5942,14 +5939,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>維持：忍者「輕身步」／武僧（Unchained）「凌波步」</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -6095,14 +6092,14 @@
           <t>沒有附英文的定名</t>
         </is>
       </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>維持：調查員「遲緩一擊」／殺手「延緩打擊」</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -8268,14 +8265,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>维持：先知「战技熟稔」／魔战士「战技精通」</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -8520,14 +8517,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>维持：炼金术师「翅膀」／术士「龙翼」</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：「翅膀」是一般用字，CHM 也沒有明確定名；龍族血統版叫「龍翼」可能是刻意區分，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -8814,14 +8811,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>牧师「酸镖」维持；法师改「酸蚀镖」</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：「酸鏢」是「強酸鏢」的一部分，內文次數沒辦法公平比較，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：不同職業的同名能力。CHM 牧師領域寫「酸鏢」，法師學派寫「酸蝕鏢」；合集包法師版寫「強酸鏢」，要改成「酸蝕鏢」（也跟 Acid→酸蝕 的決定一致）。</t>
         </is>
       </c>
     </row>
@@ -9360,14 +9357,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>维持：炼金术师「毒性抗力」／调查员「毒素抗力」</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -9402,14 +9399,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>维持：牧师「恍惚接触」／法师「眩目之触」</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -9780,14 +9777,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>飞檐走壁</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版建議「飛簷走壁」：CHM v2.33.0 寫「飛簷走壁（Nimble Climber）」2 次。</t>
         </is>
       </c>
     </row>
@@ -9990,14 +9987,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>维持：秘学士「瞬时加速」／武僧（Unchained）「电瞬步」</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -10116,14 +10113,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>维持：术士「异怪形态」／血脉狂怒者「化身异怪」</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -10452,14 +10449,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>维持：法师「生命视野」／萨满「感知生命」</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -10494,14 +10491,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>维持：忍者「轻身步」／武僧（Unchained）「凌波步」</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>
@@ -10620,14 +10617,14 @@
           <t>繁體版也有同樣的問題</t>
         </is>
       </c>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>待裁定</t>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>维持：调查员「迟缓一击」／杀手「延缓打击」</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>繁體版同一條也是待裁定：兩種說法使用次數差不多，內文也看不出哪個常用，需要人來決定。</t>
+          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
         </is>
       </c>
     </row>

--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>已裁定（42 條）。維護者 2026-10-17 回覆決定的譯名。</t>
+          <t>已裁定（46 條）。維護者 2026-10-17 回覆決定的譯名。</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>有建議譯名（100 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
+          <t>有建議譯名（96 條）。建議只從倉庫裡現有的寫法挑，不另外發明。</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3129,12 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>維持：先知「戰技熟稔」／魔戰士「戰技精通」</t>
+          <t>戰技熟稔</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）先知與魔戰士版核心效果相同（指定戰技以職業等級當基本攻擊加值），統一用「戰技熟稔」；不用「戰技精通」，因為「精通」已用來翻 Improved。</t>
         </is>
       </c>
     </row>
@@ -3179,14 +3179,14 @@
 徒手擊打×2</t>
         </is>
       </c>
-      <c r="I49" s="13" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>徒手打擊</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
+          <t>已裁定（2026-10-17）。維持 CHM 定名「徒手打擊」，不採二版的「無武裝打擊」（二版的「打擊」是動作名，一版沒有這個規則；CHM 全書「徒手打擊」698 處）。合集包的「徒手擊打」統一改掉；CHM 與合集包中指徒手攻擊的「無武裝」也改成「徒手打擊」。</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（沉淪註記：效果基本一致就用同一個譯名。）各職業版本的飛行規則不同，看起來不一樣，維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>牧師「酸鏢」維持；法師改「酸蝕鏢」</t>
+          <t>酸蝕鏢</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：不同職業的同名能力。CHM 牧師領域寫「酸鏢」，法師學派寫「酸蝕鏢」；合集包法師版寫「強酸鏢」，要改成「酸蝕鏢」（也跟 Acid→酸蝕 的決定一致）。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）牧師與法師版只差計次屬性，統一用「酸蝕鏢」，跟 Acid→酸蝕 一致。</t>
         </is>
       </c>
     </row>
@@ -4252,14 +4252,14 @@
           <t>怖懼狂嚎×10</t>
         </is>
       </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>怖懼狂嚎</t>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>驚駭狂嚎</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
+          <t>已裁定（2026-10-17，沉淪改定）。CHM 寫「怖懼狂嚎」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4561,12 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>維持：鍊金術師「毒性抗力」／調查員「毒素抗力」</t>
+          <t>毒性抗力</t>
         </is>
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）鍊金術師與調查員版只差免疫的等級，統一用 CHM 較常見的「毒性抗力」。</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>維持：牧師「恍惚接觸」／法師「眩目之觸」</t>
+          <t>暈眩之觸</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）牧師與法師版效果相同，都是讓目標暈眩（Dazed）1 輪；原本的「恍惚」是 Staggered、「眩目」像 Dazzled，容易誤會，另取新名「暈眩之觸」（維護者同意）。</t>
         </is>
       </c>
     </row>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>維持：秘學士「瞬時加速」／武僧（Unchained）「電瞬步」</t>
+          <t>瞬時加速</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）秘學士與武僧（Unchained）版效果相同（+30 尺 1 分鐘），統一用「瞬時加速」。</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>維持：術士「異怪形態」／血脈狂怒者「化身異怪」</t>
+          <t>異怪形態</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）術士與血脈狂怒者版只差傷害減免數值，統一用「異怪形態」。</t>
         </is>
       </c>
     </row>
@@ -5735,14 +5735,14 @@
           <t>高等狩獵目標×4</t>
         </is>
       </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>高等狩獵目標</t>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>精通狩獵目標</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
+          <t>已裁定（2026-10-17，沉淪改定）。專長慣例 Improved＝精通、Greater＝高等。CHM 寫「高等狩獵目標」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -5786,14 +5786,14 @@
           <t>狂怒激發×2</t>
         </is>
       </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>狂怒激發</t>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>激發凶性</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
+          <t>已裁定（2026-10-17，沉淪改定）。CHM 寫「狂怒激發」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（薩滿是看健康狀態，法師是對活物的盲視），維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（忍者是整輪雙倍移動踏過任何表面，武僧是開輕羽衡時無視困難地形），維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t>已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（殺手減半速度，調查員每次 -5 尺可疊加），維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>维持：先知「战技熟稔」／魔战士「战技精通」</t>
+          <t>战技熟稔</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）先知與魔戰士版核心效果相同（指定戰技以職業等級當基本攻擊加值），統一用「戰技熟稔」；不用「戰技精通」，因為「精通」已用來翻 Improved。</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版建議「徒手打擊」：CHM v2.33.0 寫「徒手打擊（Unarmed Strike）」22 次。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17）。維持 CHM 定名「徒手打擊」，不採二版的「無武裝打擊」（二版的「打擊」是動作名，一版沒有這個規則；CHM 全書「徒手打擊」698 處）。合集包的「徒手擊打」統一改掉；CHM 與合集包中指徒手攻擊的「無武裝」也改成「徒手打擊」。</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（沉淪註記：效果基本一致就用同一個譯名。）各職業版本的飛行規則不同，看起來不一樣，維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>牧师「酸镖」维持；法师改「酸蚀镖」</t>
+          <t>酸蚀镖</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：不同職業的同名能力。CHM 牧師領域寫「酸鏢」，法師學派寫「酸蝕鏢」；合集包法師版寫「強酸鏢」，要改成「酸蝕鏢」（也跟 Acid→酸蝕 的決定一致）。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）牧師與法師版只差計次屬性，統一用「酸蝕鏢」，跟 Acid→酸蝕 一致。</t>
         </is>
       </c>
     </row>
@@ -9107,12 +9107,12 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>怖惧狂嚎</t>
+          <t>惊骇狂嚎</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版建議「怖懼狂嚎」：CHM v2.33.0 寫「怖懼狂嚎（Terrifying Howl）」10 次。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪改定）。CHM 寫「怖懼狂嚎」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>维持：炼金术师「毒性抗力」／调查员「毒素抗力」</t>
+          <t>毒性抗力</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）鍊金術師與調查員版只差免疫的等級，統一用 CHM 較常見的「毒性抗力」。</t>
         </is>
       </c>
     </row>
@@ -9401,12 +9401,12 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>维持：牧师「恍惚接触」／法师「眩目之触」</t>
+          <t>晕眩之触</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）牧師與法師版效果相同，都是讓目標暈眩（Dazed）1 輪；原本的「恍惚」是 Staggered、「眩目」像 Dazzled，容易誤會，另取新名「暈眩之觸」（維護者同意）。</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>维持：秘学士「瞬时加速」／武僧（Unchained）「电瞬步」</t>
+          <t>瞬时加速</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）秘學士與武僧（Unchained）版效果相同（+30 尺 1 分鐘），統一用「瞬時加速」。</t>
         </is>
       </c>
     </row>
@@ -10115,12 +10115,12 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>维持：术士「异怪形态」／血脉狂怒者「化身异怪」</t>
+          <t>异怪形态</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪註記：效果基本一致就用同一個譯名。）術士與血脈狂怒者版只差傷害減免數值，統一用「異怪形態」。</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>高等狩猎目标</t>
+          <t>精通狩猎目标</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版建議「高等狩獵目標」：CHM v2.33.0 寫「高等狩獵目標（Improved Quarry）」4 次。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪改定）。專長慣例 Improved＝精通、Greater＝高等。CHM 寫「高等狩獵目標」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10367,12 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>狂怒激发</t>
+          <t>激发凶性</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版建議「狂怒激發」：CHM v2.33.0 寫「狂怒激發（Inspire Ferocity）」2 次。</t>
+          <t>跟繁體版同一條，繁體版已裁定（2026-10-17，沉淪改定）。CHM 寫「狂怒激發」，要回報 CHM。</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（薩滿是看健康狀態，法師是對活物的盲視），維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（忍者是整輪雙倍移動踏過任何表面，武僧是開輕羽衡時無視困難地形），維持不同名字。</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>跟繁體版同一條，繁體版已裁定，照 CHM：這是不同職業剛好同名的能力，CHM 本來就依職業各取各的名字，現有寫法跟 CHM 一致，維持不動。</t>
+          <t>跟繁體版同一條，繁體版已裁定（沉淪註記：效果基本一致就用同一個譯名。）效果明顯不同（殺手減半速度，調查員每次 -5 尺可疊加），維持不同名字。</t>
         </is>
       </c>
     </row>

--- a/audit/譯名一致性稽核.xlsx
+++ b/audit/譯名一致性稽核.xlsx
@@ -896,12 +896,12 @@
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>能量流失</t>
+          <t>能量吸取</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>已裁定。CHM 目前寫「能量吸取」（全文約 127 處），也要跟著改。</t>
+          <t>已裁定（2026-10-20 改定，原定「能量流失」）。跟 CHM、怪物能力 Energy Drain 用同一個詞，玩家看到「能量吸取」才查得到這個狀態；Ability Drain「屬性吸取」也一致。</t>
         </is>
       </c>
     </row>
